--- a/goldStandard/_Assessment.xlsx
+++ b/goldStandard/_Assessment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A1ADB8-295D-4065-AFDE-15C0DB953DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55FD164-E9C3-4F72-96B8-A3A10797309D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{47C0CA8E-5BD4-46FF-B103-6FF28F611458}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="19365" windowHeight="15240" xr2:uid="{47C0CA8E-5BD4-46FF-B103-6FF28F611458}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="170">
   <si>
     <t>Number</t>
   </si>
@@ -515,9 +515,6 @@
     <t>Log;Mean;TI</t>
   </si>
   <si>
-    <t>Log;Mean:TI</t>
-  </si>
-  <si>
     <t>RLR;Log</t>
   </si>
   <si>
@@ -789,7 +786,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -861,7 +858,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1184,19 +1180,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A80D0F-1143-419D-8EB5-7ABD2C3B1965}">
   <dimension ref="A1:N109"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" customWidth="1"/>
-    <col min="3" max="3" width="15.15234375" customWidth="1"/>
-    <col min="7" max="7" width="11.3828125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="66.15234375" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="66.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1240,7 +1236,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="36.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" ht="36.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="17"/>
       <c r="C2" s="42" t="s">
@@ -1274,7 +1270,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="24">
         <v>75</v>
       </c>
@@ -1324,7 +1320,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>11</v>
       </c>
@@ -1374,7 +1370,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>17</v>
       </c>
@@ -1424,7 +1420,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>98</v>
       </c>
@@ -1472,7 +1468,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>72</v>
       </c>
@@ -1522,7 +1518,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="30">
         <v>15</v>
       </c>
@@ -1572,7 +1568,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1620,7 +1616,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -1667,7 +1663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>96</v>
       </c>
@@ -1717,7 +1713,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>4</v>
       </c>
@@ -1767,7 +1763,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>20</v>
       </c>
@@ -1817,7 +1813,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>76</v>
       </c>
@@ -1864,7 +1860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>79</v>
       </c>
@@ -1911,7 +1907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
         <v>80</v>
       </c>
@@ -1946,7 +1942,7 @@
         <v>Quantile</v>
       </c>
       <c r="J16" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K16" s="30" t="s">
         <v>112</v>
@@ -1958,7 +1954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>85</v>
       </c>
@@ -2005,7 +2001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>12</v>
       </c>
@@ -2052,7 +2048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="30">
         <v>16</v>
       </c>
@@ -2087,7 +2083,7 @@
         <v>Quantile</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K19" s="30" t="s">
         <v>157</v>
@@ -2099,7 +2095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="30">
         <v>18</v>
       </c>
@@ -2146,7 +2142,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>77</v>
       </c>
@@ -2193,7 +2189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>99</v>
       </c>
@@ -2238,7 +2234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>19</v>
       </c>
@@ -2285,7 +2281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>41</v>
       </c>
@@ -2332,7 +2328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>73</v>
       </c>
@@ -2379,7 +2375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="30">
         <v>74</v>
       </c>
@@ -2426,7 +2422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>82</v>
       </c>
@@ -2473,7 +2469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>83</v>
       </c>
@@ -2518,7 +2514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="30">
         <v>84</v>
       </c>
@@ -2565,7 +2561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
         <v>88</v>
       </c>
@@ -2612,7 +2608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="30">
         <v>90</v>
       </c>
@@ -2659,7 +2655,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>93</v>
       </c>
@@ -2706,7 +2702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>95</v>
       </c>
@@ -2753,7 +2749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>7</v>
       </c>
@@ -2800,7 +2796,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>13</v>
       </c>
@@ -2838,7 +2834,7 @@
         <v>136</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L35" s="8">
         <v>6</v>
@@ -2847,7 +2843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>78</v>
       </c>
@@ -2894,7 +2890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>81</v>
       </c>
@@ -2941,7 +2937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="34">
         <v>86</v>
       </c>
@@ -2988,7 +2984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="30">
         <v>87</v>
       </c>
@@ -3026,7 +3022,7 @@
         <v>145</v>
       </c>
       <c r="K39" s="30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L39" s="26">
         <v>7</v>
@@ -3035,7 +3031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="30">
         <v>89</v>
       </c>
@@ -3082,7 +3078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="30">
         <v>94</v>
       </c>
@@ -3120,7 +3116,7 @@
         <v>142</v>
       </c>
       <c r="K41" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L41" s="26">
         <v>7</v>
@@ -3129,7 +3125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>1</v>
       </c>
@@ -3176,7 +3172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="30">
         <v>2</v>
       </c>
@@ -3223,7 +3219,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>3</v>
       </c>
@@ -3258,7 +3254,7 @@
         <v>Quantile</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>112</v>
@@ -3270,7 +3266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>8</v>
       </c>
@@ -3315,7 +3311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>92</v>
       </c>
@@ -3362,7 +3358,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>97</v>
       </c>
@@ -3407,7 +3403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>10</v>
       </c>
@@ -3452,7 +3448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>14</v>
       </c>
@@ -3499,7 +3495,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="30">
         <v>91</v>
       </c>
@@ -3546,7 +3542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="30">
         <v>100</v>
       </c>
@@ -3591,7 +3587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="30">
         <v>9</v>
       </c>
@@ -3638,7 +3634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="20">
         <v>36</v>
       </c>
@@ -3685,7 +3681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>32</v>
       </c>
@@ -3732,7 +3728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -3779,7 +3775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>29</v>
       </c>
@@ -3824,7 +3820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>26</v>
       </c>
@@ -3869,7 +3865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>27</v>
       </c>
@@ -3914,7 +3910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="30">
         <v>48</v>
       </c>
@@ -3961,7 +3957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="30">
         <v>53</v>
       </c>
@@ -4006,7 +4002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="30">
         <v>58</v>
       </c>
@@ -4044,7 +4040,7 @@
         <v>118</v>
       </c>
       <c r="K61" s="26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L61" s="27">
         <v>2</v>
@@ -4053,7 +4049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="30">
         <v>62</v>
       </c>
@@ -4098,7 +4094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="30">
         <v>63</v>
       </c>
@@ -4145,7 +4141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="30">
         <v>68</v>
       </c>
@@ -4192,7 +4188,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>33</v>
       </c>
@@ -4239,7 +4235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>37</v>
       </c>
@@ -4284,7 +4280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>59</v>
       </c>
@@ -4329,7 +4325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>22</v>
       </c>
@@ -4374,7 +4370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>23</v>
       </c>
@@ -4419,7 +4415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>56</v>
       </c>
@@ -4466,7 +4462,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="30">
         <v>55</v>
       </c>
@@ -4511,7 +4507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="30">
         <v>57</v>
       </c>
@@ -4558,7 +4554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="30">
         <v>60</v>
       </c>
@@ -4605,7 +4601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="30">
         <v>61</v>
       </c>
@@ -4652,7 +4648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="30">
         <v>64</v>
       </c>
@@ -4697,7 +4693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>65</v>
       </c>
@@ -4744,7 +4740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>43</v>
       </c>
@@ -4791,7 +4787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>44</v>
       </c>
@@ -4826,7 +4822,7 @@
         <v>Quantile</v>
       </c>
       <c r="J78" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K78" s="8" t="s">
         <v>131</v>
@@ -4838,7 +4834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>46</v>
       </c>
@@ -4885,7 +4881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>49</v>
       </c>
@@ -4932,7 +4928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>51</v>
       </c>
@@ -4970,7 +4966,7 @@
         <v>116</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L81">
         <v>5</v>
@@ -4979,7 +4975,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="30">
         <v>71</v>
       </c>
@@ -5024,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="30">
         <v>47</v>
       </c>
@@ -5069,7 +5065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="30">
         <v>34</v>
       </c>
@@ -5114,7 +5110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="30">
         <v>42</v>
       </c>
@@ -5159,7 +5155,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="30">
         <v>52</v>
       </c>
@@ -5194,7 +5190,7 @@
         <v>Quantile</v>
       </c>
       <c r="J86" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K86" s="26" t="s">
         <v>157</v>
@@ -5206,7 +5202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="30">
         <v>69</v>
       </c>
@@ -5253,7 +5249,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>21</v>
       </c>
@@ -5288,7 +5284,7 @@
         <v>Median</v>
       </c>
       <c r="J88" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K88" s="8"/>
       <c r="L88">
@@ -5298,7 +5294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>45</v>
       </c>
@@ -5345,7 +5341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>50</v>
       </c>
@@ -5390,7 +5386,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>30</v>
       </c>
@@ -5435,7 +5431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>70</v>
       </c>
@@ -5482,7 +5478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>35</v>
       </c>
@@ -5527,7 +5523,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="30">
         <v>28</v>
       </c>
@@ -5572,7 +5568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="30">
         <v>31</v>
       </c>
@@ -5617,7 +5613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="30">
         <v>40</v>
       </c>
@@ -5652,7 +5648,7 @@
         <v>Quantile</v>
       </c>
       <c r="J96" s="27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K96" s="26" t="s">
         <v>132</v>
@@ -5664,7 +5660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="30">
         <v>66</v>
       </c>
@@ -5711,7 +5707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="30">
         <v>67</v>
       </c>
@@ -5756,7 +5752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="30">
         <v>24</v>
       </c>
@@ -5801,14 +5797,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>25</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C100" s="43" t="s">
+      <c r="C100" t="s">
         <v>122</v>
       </c>
       <c r="D100" s="3" t="str">
@@ -5846,7 +5842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>39</v>
       </c>
@@ -5893,7 +5889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>38</v>
       </c>
@@ -5938,7 +5934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B109" s="1"/>
     </row>
   </sheetData>
@@ -5950,22 +5946,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0EB6134-0119-406C-9590-2A2C09D09120}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -6000,7 +5996,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="30">
         <v>75</v>
       </c>
@@ -6035,7 +6031,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>11</v>
       </c>
@@ -6070,7 +6066,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>17</v>
       </c>
@@ -6105,7 +6101,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>98</v>
       </c>
@@ -6140,7 +6136,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>72</v>
       </c>
@@ -6175,7 +6171,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>15</v>
       </c>
@@ -6210,7 +6206,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -6245,7 +6241,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -6280,7 +6276,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>96</v>
       </c>
@@ -6315,7 +6311,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -6350,7 +6346,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>20</v>
       </c>
@@ -6385,7 +6381,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>76</v>
       </c>
@@ -6420,7 +6416,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
         <v>79</v>
       </c>
@@ -6455,7 +6451,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>80</v>
       </c>
@@ -6490,7 +6486,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
         <v>85</v>
       </c>
@@ -6525,7 +6521,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>12</v>
       </c>
@@ -6560,7 +6556,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>16</v>
       </c>
@@ -6595,7 +6591,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="30">
         <v>18</v>
       </c>
@@ -6630,7 +6626,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>77</v>
       </c>
@@ -6665,7 +6661,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>99</v>
       </c>
@@ -6700,7 +6696,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>19</v>
       </c>
@@ -6735,7 +6731,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>41</v>
       </c>
@@ -6770,7 +6766,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>73</v>
       </c>
@@ -6805,7 +6801,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>74</v>
       </c>
@@ -6840,7 +6836,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="30">
         <v>82</v>
       </c>
@@ -6875,7 +6871,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>83</v>
       </c>
@@ -6910,7 +6906,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="30">
         <v>84</v>
       </c>
@@ -6945,7 +6941,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="30">
         <v>88</v>
       </c>
@@ -6980,7 +6976,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
         <v>90</v>
       </c>
@@ -7015,7 +7011,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>93</v>
       </c>
@@ -7050,7 +7046,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>95</v>
       </c>
@@ -7085,7 +7081,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>7</v>
       </c>
@@ -7120,7 +7116,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>13</v>
       </c>
@@ -7155,7 +7151,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>78</v>
       </c>
@@ -7190,7 +7186,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>81</v>
       </c>
@@ -7225,7 +7221,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="34">
         <v>86</v>
       </c>
@@ -7260,7 +7256,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="30">
         <v>87</v>
       </c>
@@ -7295,7 +7291,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="30">
         <v>89</v>
       </c>
@@ -7330,7 +7326,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="30">
         <v>94</v>
       </c>
@@ -7365,7 +7361,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="30">
         <v>1</v>
       </c>
@@ -7400,7 +7396,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>2</v>
       </c>
@@ -7435,7 +7431,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>3</v>
       </c>
@@ -7470,7 +7466,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>8</v>
       </c>
@@ -7505,7 +7501,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>92</v>
       </c>
@@ -7540,7 +7536,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>97</v>
       </c>
@@ -7575,7 +7571,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>10</v>
       </c>
@@ -7610,7 +7606,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>14</v>
       </c>
@@ -7645,7 +7641,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="30">
         <v>91</v>
       </c>
@@ -7680,7 +7676,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="30">
         <v>100</v>
       </c>
@@ -7715,7 +7711,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="30">
         <v>9</v>
       </c>
@@ -7750,7 +7746,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>36</v>
       </c>
@@ -7785,7 +7781,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>32</v>
       </c>
@@ -7820,7 +7816,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>54</v>
       </c>
@@ -7855,7 +7851,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>29</v>
       </c>
@@ -7890,7 +7886,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>26</v>
       </c>
@@ -7925,7 +7921,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>27</v>
       </c>
@@ -7960,7 +7956,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="30">
         <v>48</v>
       </c>
@@ -7995,7 +7991,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="30">
         <v>53</v>
       </c>
@@ -8030,7 +8026,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="30">
         <v>58</v>
       </c>
@@ -8065,7 +8061,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="30">
         <v>62</v>
       </c>
@@ -8100,7 +8096,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="30">
         <v>63</v>
       </c>
@@ -8135,7 +8131,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="30">
         <v>68</v>
       </c>
@@ -8170,7 +8166,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>33</v>
       </c>
@@ -8205,7 +8201,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>37</v>
       </c>
@@ -8240,7 +8236,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>59</v>
       </c>
@@ -8275,7 +8271,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>22</v>
       </c>
@@ -8310,7 +8306,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>23</v>
       </c>
@@ -8345,7 +8341,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>56</v>
       </c>
@@ -8380,7 +8376,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="30">
         <v>55</v>
       </c>
@@ -8415,7 +8411,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="30">
         <v>57</v>
       </c>
@@ -8450,7 +8446,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="30">
         <v>60</v>
       </c>
@@ -8485,7 +8481,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="30">
         <v>61</v>
       </c>
@@ -8520,7 +8516,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="30">
         <v>64</v>
       </c>
@@ -8555,7 +8551,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>65</v>
       </c>
@@ -8590,7 +8586,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>43</v>
       </c>
@@ -8625,7 +8621,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>44</v>
       </c>
@@ -8660,7 +8656,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>46</v>
       </c>
@@ -8695,7 +8691,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>49</v>
       </c>
@@ -8730,7 +8726,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>51</v>
       </c>
@@ -8765,7 +8761,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="30">
         <v>71</v>
       </c>
@@ -8800,7 +8796,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="30">
         <v>47</v>
       </c>
@@ -8835,7 +8831,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="30">
         <v>34</v>
       </c>
@@ -8870,7 +8866,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="30">
         <v>42</v>
       </c>
@@ -8905,7 +8901,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="30">
         <v>52</v>
       </c>
@@ -8940,7 +8936,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="30">
         <v>69</v>
       </c>
@@ -8975,7 +8971,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>21</v>
       </c>
@@ -9010,7 +9006,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>45</v>
       </c>
@@ -9045,7 +9041,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>50</v>
       </c>
@@ -9080,7 +9076,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>30</v>
       </c>
@@ -9115,7 +9111,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>70</v>
       </c>
@@ -9150,7 +9146,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>35</v>
       </c>
@@ -9185,7 +9181,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="30">
         <v>28</v>
       </c>
@@ -9220,7 +9216,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="30">
         <v>31</v>
       </c>
@@ -9255,7 +9251,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="30">
         <v>40</v>
       </c>
@@ -9290,7 +9286,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="30">
         <v>66</v>
       </c>
@@ -9325,7 +9321,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="30">
         <v>67</v>
       </c>
@@ -9360,7 +9356,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="30">
         <v>24</v>
       </c>
@@ -9395,7 +9391,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>25</v>
       </c>
@@ -9430,7 +9426,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>39</v>
       </c>
@@ -9465,7 +9461,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>38</v>
       </c>
@@ -9508,22 +9504,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5238B6DF-21B6-4EF8-9EB1-9E4E52C8D26E}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -9558,7 +9554,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="30">
         <v>75</v>
       </c>
@@ -9593,7 +9589,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>11</v>
       </c>
@@ -9628,7 +9624,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>17</v>
       </c>
@@ -9663,7 +9659,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>98</v>
       </c>
@@ -9698,7 +9694,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>72</v>
       </c>
@@ -9733,7 +9729,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>15</v>
       </c>
@@ -9768,7 +9764,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -9803,7 +9799,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -9838,7 +9834,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>96</v>
       </c>
@@ -9873,7 +9869,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -9908,7 +9904,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>20</v>
       </c>
@@ -9943,7 +9939,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>76</v>
       </c>
@@ -9978,7 +9974,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
         <v>79</v>
       </c>
@@ -10013,7 +10009,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>80</v>
       </c>
@@ -10048,7 +10044,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
         <v>85</v>
       </c>
@@ -10083,7 +10079,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>12</v>
       </c>
@@ -10118,7 +10114,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>16</v>
       </c>
@@ -10153,7 +10149,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="30">
         <v>18</v>
       </c>
@@ -10188,7 +10184,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>77</v>
       </c>
@@ -10223,7 +10219,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>99</v>
       </c>
@@ -10258,7 +10254,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>19</v>
       </c>
@@ -10293,7 +10289,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>41</v>
       </c>
@@ -10328,7 +10324,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>73</v>
       </c>
@@ -10363,7 +10359,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>74</v>
       </c>
@@ -10398,7 +10394,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="30">
         <v>82</v>
       </c>
@@ -10433,7 +10429,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>83</v>
       </c>
@@ -10468,7 +10464,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="30">
         <v>84</v>
       </c>
@@ -10503,7 +10499,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="30">
         <v>88</v>
       </c>
@@ -10538,7 +10534,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
         <v>90</v>
       </c>
@@ -10573,7 +10569,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>93</v>
       </c>
@@ -10608,7 +10604,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>95</v>
       </c>
@@ -10643,7 +10639,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>7</v>
       </c>
@@ -10678,7 +10674,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>13</v>
       </c>
@@ -10713,7 +10709,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>78</v>
       </c>
@@ -10748,7 +10744,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>81</v>
       </c>
@@ -10783,7 +10779,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="34">
         <v>86</v>
       </c>
@@ -10818,7 +10814,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="30">
         <v>87</v>
       </c>
@@ -10853,7 +10849,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="30">
         <v>89</v>
       </c>
@@ -10888,7 +10884,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="30">
         <v>94</v>
       </c>
@@ -10923,7 +10919,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="30">
         <v>1</v>
       </c>
@@ -10958,7 +10954,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>2</v>
       </c>
@@ -10993,7 +10989,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>3</v>
       </c>
@@ -11028,7 +11024,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>8</v>
       </c>
@@ -11063,7 +11059,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>92</v>
       </c>
@@ -11098,7 +11094,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>97</v>
       </c>
@@ -11133,7 +11129,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>10</v>
       </c>
@@ -11168,7 +11164,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>14</v>
       </c>
@@ -11203,7 +11199,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="30">
         <v>91</v>
       </c>
@@ -11238,7 +11234,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="30">
         <v>100</v>
       </c>
@@ -11273,7 +11269,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="30">
         <v>9</v>
       </c>
@@ -11308,7 +11304,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>36</v>
       </c>
@@ -11343,7 +11339,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>32</v>
       </c>
@@ -11378,7 +11374,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>54</v>
       </c>
@@ -11413,7 +11409,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>29</v>
       </c>
@@ -11448,7 +11444,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>26</v>
       </c>
@@ -11483,7 +11479,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>27</v>
       </c>
@@ -11518,7 +11514,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="30">
         <v>48</v>
       </c>
@@ -11553,7 +11549,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="30">
         <v>53</v>
       </c>
@@ -11588,7 +11584,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="30">
         <v>58</v>
       </c>
@@ -11623,7 +11619,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="30">
         <v>62</v>
       </c>
@@ -11658,7 +11654,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="30">
         <v>63</v>
       </c>
@@ -11693,7 +11689,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="30">
         <v>68</v>
       </c>
@@ -11728,7 +11724,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>33</v>
       </c>
@@ -11763,7 +11759,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>37</v>
       </c>
@@ -11798,7 +11794,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>59</v>
       </c>
@@ -11833,7 +11829,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>22</v>
       </c>
@@ -11868,7 +11864,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>23</v>
       </c>
@@ -11903,7 +11899,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>56</v>
       </c>
@@ -11938,7 +11934,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="30">
         <v>55</v>
       </c>
@@ -11973,7 +11969,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="30">
         <v>57</v>
       </c>
@@ -12008,7 +12004,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="30">
         <v>60</v>
       </c>
@@ -12043,7 +12039,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="30">
         <v>61</v>
       </c>
@@ -12078,7 +12074,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="30">
         <v>64</v>
       </c>
@@ -12113,7 +12109,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>65</v>
       </c>
@@ -12148,7 +12144,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>43</v>
       </c>
@@ -12183,7 +12179,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>44</v>
       </c>
@@ -12218,7 +12214,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>46</v>
       </c>
@@ -12253,7 +12249,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>49</v>
       </c>
@@ -12288,7 +12284,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>51</v>
       </c>
@@ -12323,7 +12319,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="30">
         <v>71</v>
       </c>
@@ -12358,7 +12354,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="30">
         <v>47</v>
       </c>
@@ -12393,7 +12389,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="30">
         <v>34</v>
       </c>
@@ -12428,7 +12424,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="30">
         <v>42</v>
       </c>
@@ -12463,7 +12459,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="30">
         <v>52</v>
       </c>
@@ -12498,7 +12494,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="30">
         <v>69</v>
       </c>
@@ -12533,7 +12529,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>21</v>
       </c>
@@ -12568,7 +12564,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>45</v>
       </c>
@@ -12603,7 +12599,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>50</v>
       </c>
@@ -12638,7 +12634,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>30</v>
       </c>
@@ -12673,7 +12669,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>70</v>
       </c>
@@ -12708,7 +12704,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>35</v>
       </c>
@@ -12743,7 +12739,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="30">
         <v>28</v>
       </c>
@@ -12778,7 +12774,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="30">
         <v>31</v>
       </c>
@@ -12813,7 +12809,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="30">
         <v>40</v>
       </c>
@@ -12848,7 +12844,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="30">
         <v>66</v>
       </c>
@@ -12883,7 +12879,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="30">
         <v>67</v>
       </c>
@@ -12918,7 +12914,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="30">
         <v>24</v>
       </c>
@@ -12953,7 +12949,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>25</v>
       </c>
@@ -12988,7 +12984,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>39</v>
       </c>
@@ -13023,7 +13019,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>38</v>
       </c>
@@ -13066,22 +13062,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CE19896-BF8D-4ED1-946F-8FB98B3BAA55}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -13116,7 +13112,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="30">
         <v>75</v>
       </c>
@@ -13151,7 +13147,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>11</v>
       </c>
@@ -13186,7 +13182,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>17</v>
       </c>
@@ -13221,7 +13217,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>98</v>
       </c>
@@ -13256,7 +13252,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>72</v>
       </c>
@@ -13291,7 +13287,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>15</v>
       </c>
@@ -13326,7 +13322,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -13361,7 +13357,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -13396,7 +13392,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>96</v>
       </c>
@@ -13431,7 +13427,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -13466,7 +13462,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>20</v>
       </c>
@@ -13501,7 +13497,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>76</v>
       </c>
@@ -13536,7 +13532,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
         <v>79</v>
       </c>
@@ -13571,7 +13567,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>80</v>
       </c>
@@ -13606,7 +13602,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
         <v>85</v>
       </c>
@@ -13641,7 +13637,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>12</v>
       </c>
@@ -13676,7 +13672,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>16</v>
       </c>
@@ -13711,7 +13707,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="30">
         <v>18</v>
       </c>
@@ -13746,7 +13742,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>77</v>
       </c>
@@ -13781,7 +13777,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>99</v>
       </c>
@@ -13816,7 +13812,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="39" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>19</v>
       </c>
@@ -13851,7 +13847,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>41</v>
       </c>
@@ -13886,7 +13882,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>73</v>
       </c>
@@ -13921,7 +13917,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>74</v>
       </c>
@@ -13956,7 +13952,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="30">
         <v>82</v>
       </c>
@@ -13991,7 +13987,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>83</v>
       </c>
@@ -14026,7 +14022,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="30">
         <v>84</v>
       </c>
@@ -14061,7 +14057,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="30">
         <v>88</v>
       </c>
@@ -14096,7 +14092,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
         <v>90</v>
       </c>
@@ -14131,7 +14127,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>93</v>
       </c>
@@ -14166,7 +14162,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>95</v>
       </c>
@@ -14201,7 +14197,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>7</v>
       </c>
@@ -14236,7 +14232,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>13</v>
       </c>
@@ -14271,7 +14267,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>78</v>
       </c>
@@ -14306,7 +14302,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>81</v>
       </c>
@@ -14341,7 +14337,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="34">
         <v>86</v>
       </c>
@@ -14376,7 +14372,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="30">
         <v>87</v>
       </c>
@@ -14411,7 +14407,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="30">
         <v>89</v>
       </c>
@@ -14446,7 +14442,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="30">
         <v>94</v>
       </c>
@@ -14481,7 +14477,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="30">
         <v>1</v>
       </c>
@@ -14516,7 +14512,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>2</v>
       </c>
@@ -14551,7 +14547,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>3</v>
       </c>
@@ -14586,7 +14582,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>8</v>
       </c>
@@ -14621,7 +14617,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>92</v>
       </c>
@@ -14656,7 +14652,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>97</v>
       </c>
@@ -14691,7 +14687,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>10</v>
       </c>
@@ -14726,7 +14722,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>14</v>
       </c>
@@ -14761,7 +14757,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="30">
         <v>91</v>
       </c>
@@ -14796,7 +14792,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="30">
         <v>100</v>
       </c>
@@ -14831,7 +14827,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="30">
         <v>9</v>
       </c>
@@ -14866,7 +14862,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>36</v>
       </c>
@@ -14901,7 +14897,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>32</v>
       </c>
@@ -14936,7 +14932,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>54</v>
       </c>
@@ -14971,7 +14967,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>29</v>
       </c>
@@ -15006,7 +15002,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>26</v>
       </c>
@@ -15041,7 +15037,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>27</v>
       </c>
@@ -15076,7 +15072,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="30">
         <v>48</v>
       </c>
@@ -15111,7 +15107,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="30">
         <v>53</v>
       </c>
@@ -15146,7 +15142,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="30">
         <v>58</v>
       </c>
@@ -15181,7 +15177,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="30">
         <v>62</v>
       </c>
@@ -15216,7 +15212,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="30">
         <v>63</v>
       </c>
@@ -15251,7 +15247,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="30">
         <v>68</v>
       </c>
@@ -15286,7 +15282,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>33</v>
       </c>
@@ -15321,7 +15317,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>37</v>
       </c>
@@ -15356,7 +15352,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>59</v>
       </c>
@@ -15391,7 +15387,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>22</v>
       </c>
@@ -15426,7 +15422,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>23</v>
       </c>
@@ -15461,7 +15457,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>56</v>
       </c>
@@ -15496,7 +15492,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="30">
         <v>55</v>
       </c>
@@ -15531,7 +15527,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="30">
         <v>57</v>
       </c>
@@ -15566,7 +15562,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="30">
         <v>60</v>
       </c>
@@ -15601,7 +15597,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="30">
         <v>61</v>
       </c>
@@ -15636,7 +15632,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="30">
         <v>64</v>
       </c>
@@ -15671,7 +15667,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>65</v>
       </c>
@@ -15706,7 +15702,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>43</v>
       </c>
@@ -15741,7 +15737,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>44</v>
       </c>
@@ -15776,7 +15772,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>46</v>
       </c>
@@ -15811,7 +15807,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>49</v>
       </c>
@@ -15846,7 +15842,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>51</v>
       </c>
@@ -15881,7 +15877,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="30">
         <v>71</v>
       </c>
@@ -15916,7 +15912,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="30">
         <v>47</v>
       </c>
@@ -15951,7 +15947,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="30">
         <v>34</v>
       </c>
@@ -15986,7 +15982,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="30">
         <v>42</v>
       </c>
@@ -16021,7 +16017,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="30">
         <v>52</v>
       </c>
@@ -16056,7 +16052,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="30">
         <v>69</v>
       </c>
@@ -16091,7 +16087,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>21</v>
       </c>
@@ -16126,7 +16122,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>45</v>
       </c>
@@ -16161,7 +16157,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>50</v>
       </c>
@@ -16196,7 +16192,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>30</v>
       </c>
@@ -16231,7 +16227,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>70</v>
       </c>
@@ -16266,7 +16262,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>35</v>
       </c>
@@ -16301,7 +16297,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="30">
         <v>28</v>
       </c>
@@ -16336,7 +16332,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="30">
         <v>31</v>
       </c>
@@ -16371,7 +16367,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="30">
         <v>40</v>
       </c>
@@ -16406,7 +16402,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="30">
         <v>66</v>
       </c>
@@ -16441,7 +16437,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="30">
         <v>67</v>
       </c>
@@ -16476,7 +16472,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="30">
         <v>24</v>
       </c>
@@ -16511,7 +16507,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>25</v>
       </c>
@@ -16546,7 +16542,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>39</v>
       </c>
@@ -16581,7 +16577,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>38</v>
       </c>
@@ -16625,22 +16621,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEF0B17-D72A-4614-98F7-4D2B4AE7F01E}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -16675,7 +16671,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="30">
         <v>75</v>
       </c>
@@ -16710,7 +16706,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>11</v>
       </c>
@@ -16745,7 +16741,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>17</v>
       </c>
@@ -16780,7 +16776,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>98</v>
       </c>
@@ -16815,7 +16811,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>72</v>
       </c>
@@ -16850,7 +16846,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>15</v>
       </c>
@@ -16885,7 +16881,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -16920,7 +16916,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -16955,7 +16951,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>96</v>
       </c>
@@ -16990,7 +16986,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -17025,7 +17021,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>20</v>
       </c>
@@ -17060,7 +17056,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>76</v>
       </c>
@@ -17095,7 +17091,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
         <v>79</v>
       </c>
@@ -17130,7 +17126,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>80</v>
       </c>
@@ -17165,7 +17161,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
         <v>85</v>
       </c>
@@ -17200,7 +17196,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>12</v>
       </c>
@@ -17235,7 +17231,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>16</v>
       </c>
@@ -17270,7 +17266,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="30">
         <v>18</v>
       </c>
@@ -17305,7 +17301,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>77</v>
       </c>
@@ -17340,7 +17336,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>99</v>
       </c>
@@ -17375,7 +17371,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>19</v>
       </c>
@@ -17410,7 +17406,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>41</v>
       </c>
@@ -17445,7 +17441,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>73</v>
       </c>
@@ -17480,7 +17476,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>74</v>
       </c>
@@ -17515,7 +17511,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="30">
         <v>82</v>
       </c>
@@ -17550,7 +17546,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>83</v>
       </c>
@@ -17585,7 +17581,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="30">
         <v>84</v>
       </c>
@@ -17620,7 +17616,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="30">
         <v>88</v>
       </c>
@@ -17655,7 +17651,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
         <v>90</v>
       </c>
@@ -17690,7 +17686,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>93</v>
       </c>
@@ -17725,7 +17721,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>95</v>
       </c>
@@ -17760,7 +17756,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>7</v>
       </c>
@@ -17795,7 +17791,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>13</v>
       </c>
@@ -17830,7 +17826,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>78</v>
       </c>
@@ -17865,7 +17861,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>81</v>
       </c>
@@ -17900,7 +17896,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="34">
         <v>86</v>
       </c>
@@ -17935,7 +17931,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="30">
         <v>87</v>
       </c>
@@ -17970,7 +17966,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="30">
         <v>89</v>
       </c>
@@ -18005,7 +18001,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="30">
         <v>94</v>
       </c>
@@ -18040,7 +18036,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="30">
         <v>1</v>
       </c>
@@ -18075,7 +18071,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>2</v>
       </c>
@@ -18110,7 +18106,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>3</v>
       </c>
@@ -18145,7 +18141,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>8</v>
       </c>
@@ -18180,7 +18176,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>92</v>
       </c>
@@ -18215,7 +18211,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>97</v>
       </c>
@@ -18250,7 +18246,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>10</v>
       </c>
@@ -18285,7 +18281,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>14</v>
       </c>
@@ -18320,7 +18316,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="30">
         <v>91</v>
       </c>
@@ -18355,7 +18351,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="30">
         <v>100</v>
       </c>
@@ -18390,7 +18386,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="30">
         <v>9</v>
       </c>
@@ -18425,7 +18421,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>36</v>
       </c>
@@ -18460,7 +18456,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>32</v>
       </c>
@@ -18495,7 +18491,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>54</v>
       </c>
@@ -18530,7 +18526,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>29</v>
       </c>
@@ -18565,7 +18561,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>26</v>
       </c>
@@ -18600,7 +18596,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>27</v>
       </c>
@@ -18635,7 +18631,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="30">
         <v>48</v>
       </c>
@@ -18670,7 +18666,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="30">
         <v>53</v>
       </c>
@@ -18705,7 +18701,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="30">
         <v>58</v>
       </c>
@@ -18740,7 +18736,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="30">
         <v>62</v>
       </c>
@@ -18775,7 +18771,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="30">
         <v>63</v>
       </c>
@@ -18810,7 +18806,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="30">
         <v>68</v>
       </c>
@@ -18845,7 +18841,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>33</v>
       </c>
@@ -18880,7 +18876,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>37</v>
       </c>
@@ -18915,7 +18911,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>59</v>
       </c>
@@ -18950,7 +18946,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>22</v>
       </c>
@@ -18985,7 +18981,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>23</v>
       </c>
@@ -19020,7 +19016,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>56</v>
       </c>
@@ -19055,7 +19051,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="30">
         <v>55</v>
       </c>
@@ -19090,7 +19086,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="30">
         <v>57</v>
       </c>
@@ -19125,7 +19121,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="30">
         <v>60</v>
       </c>
@@ -19160,7 +19156,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="30">
         <v>61</v>
       </c>
@@ -19195,7 +19191,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="30">
         <v>64</v>
       </c>
@@ -19230,7 +19226,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>65</v>
       </c>
@@ -19265,7 +19261,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>43</v>
       </c>
@@ -19300,7 +19296,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>44</v>
       </c>
@@ -19335,7 +19331,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>46</v>
       </c>
@@ -19370,7 +19366,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>49</v>
       </c>
@@ -19405,7 +19401,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>51</v>
       </c>
@@ -19440,7 +19436,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="30">
         <v>71</v>
       </c>
@@ -19475,7 +19471,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="30">
         <v>47</v>
       </c>
@@ -19510,7 +19506,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="30">
         <v>34</v>
       </c>
@@ -19545,7 +19541,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="30">
         <v>42</v>
       </c>
@@ -19580,7 +19576,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="30">
         <v>52</v>
       </c>
@@ -19615,7 +19611,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="30">
         <v>69</v>
       </c>
@@ -19650,7 +19646,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>21</v>
       </c>
@@ -19685,7 +19681,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>45</v>
       </c>
@@ -19720,7 +19716,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>50</v>
       </c>
@@ -19755,7 +19751,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>30</v>
       </c>
@@ -19790,7 +19786,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>70</v>
       </c>
@@ -19825,7 +19821,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>35</v>
       </c>
@@ -19860,7 +19856,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="30">
         <v>28</v>
       </c>
@@ -19895,7 +19891,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="30">
         <v>31</v>
       </c>
@@ -19930,7 +19926,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="30">
         <v>40</v>
       </c>
@@ -19965,7 +19961,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="30">
         <v>66</v>
       </c>
@@ -20000,7 +19996,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="30">
         <v>67</v>
       </c>
@@ -20035,7 +20031,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="30">
         <v>24</v>
       </c>
@@ -20070,7 +20066,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>25</v>
       </c>
@@ -20105,7 +20101,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>39</v>
       </c>
@@ -20140,7 +20136,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>38</v>
       </c>
@@ -20183,22 +20179,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A1124C-281A-4167-9729-37CAB9C0D70A}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -20233,7 +20229,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="30">
         <v>75</v>
       </c>
@@ -20268,7 +20264,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>11</v>
       </c>
@@ -20303,7 +20299,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>17</v>
       </c>
@@ -20338,7 +20334,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>98</v>
       </c>
@@ -20373,7 +20369,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>72</v>
       </c>
@@ -20408,7 +20404,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>15</v>
       </c>
@@ -20443,7 +20439,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -20478,7 +20474,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -20513,7 +20509,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>96</v>
       </c>
@@ -20548,7 +20544,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -20583,7 +20579,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>20</v>
       </c>
@@ -20618,7 +20614,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>76</v>
       </c>
@@ -20653,7 +20649,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
         <v>79</v>
       </c>
@@ -20688,7 +20684,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>80</v>
       </c>
@@ -20723,7 +20719,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
         <v>85</v>
       </c>
@@ -20758,7 +20754,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>12</v>
       </c>
@@ -20793,7 +20789,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>16</v>
       </c>
@@ -20828,7 +20824,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="30">
         <v>18</v>
       </c>
@@ -20863,7 +20859,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>77</v>
       </c>
@@ -20898,7 +20894,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>99</v>
       </c>
@@ -20933,7 +20929,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>19</v>
       </c>
@@ -20968,7 +20964,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>41</v>
       </c>
@@ -21003,7 +20999,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>73</v>
       </c>
@@ -21038,7 +21034,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>74</v>
       </c>
@@ -21073,7 +21069,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="30">
         <v>82</v>
       </c>
@@ -21108,7 +21104,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>83</v>
       </c>
@@ -21143,7 +21139,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="30">
         <v>84</v>
       </c>
@@ -21178,7 +21174,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="30">
         <v>88</v>
       </c>
@@ -21213,7 +21209,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
         <v>90</v>
       </c>
@@ -21248,7 +21244,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>93</v>
       </c>
@@ -21283,7 +21279,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>95</v>
       </c>
@@ -21318,7 +21314,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>7</v>
       </c>
@@ -21353,7 +21349,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>13</v>
       </c>
@@ -21388,7 +21384,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>78</v>
       </c>
@@ -21423,7 +21419,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>81</v>
       </c>
@@ -21458,7 +21454,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="34">
         <v>86</v>
       </c>
@@ -21493,7 +21489,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="30">
         <v>87</v>
       </c>
@@ -21528,7 +21524,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="30">
         <v>89</v>
       </c>
@@ -21563,7 +21559,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="30">
         <v>94</v>
       </c>
@@ -21598,7 +21594,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="30">
         <v>1</v>
       </c>
@@ -21633,7 +21629,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>2</v>
       </c>
@@ -21668,7 +21664,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>3</v>
       </c>
@@ -21703,7 +21699,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>8</v>
       </c>
@@ -21738,7 +21734,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>92</v>
       </c>
@@ -21773,7 +21769,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>97</v>
       </c>
@@ -21808,7 +21804,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>10</v>
       </c>
@@ -21843,7 +21839,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>14</v>
       </c>
@@ -21878,7 +21874,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="30">
         <v>91</v>
       </c>
@@ -21913,7 +21909,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="30">
         <v>100</v>
       </c>
@@ -21948,7 +21944,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="30">
         <v>9</v>
       </c>
@@ -21983,7 +21979,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>36</v>
       </c>
@@ -22018,7 +22014,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>32</v>
       </c>
@@ -22053,7 +22049,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>54</v>
       </c>
@@ -22088,7 +22084,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>29</v>
       </c>
@@ -22123,7 +22119,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>26</v>
       </c>
@@ -22158,7 +22154,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>27</v>
       </c>
@@ -22193,7 +22189,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="30">
         <v>48</v>
       </c>
@@ -22228,7 +22224,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="30">
         <v>53</v>
       </c>
@@ -22263,7 +22259,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="30">
         <v>58</v>
       </c>
@@ -22298,7 +22294,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="30">
         <v>62</v>
       </c>
@@ -22333,7 +22329,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="30">
         <v>63</v>
       </c>
@@ -22368,7 +22364,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="30">
         <v>68</v>
       </c>
@@ -22403,7 +22399,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>33</v>
       </c>
@@ -22438,7 +22434,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>37</v>
       </c>
@@ -22473,7 +22469,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>59</v>
       </c>
@@ -22508,7 +22504,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>22</v>
       </c>
@@ -22543,7 +22539,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>23</v>
       </c>
@@ -22578,7 +22574,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>56</v>
       </c>
@@ -22613,7 +22609,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="30">
         <v>55</v>
       </c>
@@ -22648,7 +22644,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="30">
         <v>57</v>
       </c>
@@ -22683,7 +22679,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="30">
         <v>60</v>
       </c>
@@ -22718,7 +22714,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="30">
         <v>61</v>
       </c>
@@ -22753,7 +22749,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="30">
         <v>64</v>
       </c>
@@ -22788,7 +22784,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>65</v>
       </c>
@@ -22823,7 +22819,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>43</v>
       </c>
@@ -22858,7 +22854,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>44</v>
       </c>
@@ -22893,7 +22889,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>46</v>
       </c>
@@ -22928,7 +22924,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>49</v>
       </c>
@@ -22963,7 +22959,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>51</v>
       </c>
@@ -22998,7 +22994,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="30">
         <v>71</v>
       </c>
@@ -23033,7 +23029,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="30">
         <v>47</v>
       </c>
@@ -23068,7 +23064,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="30">
         <v>34</v>
       </c>
@@ -23103,7 +23099,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="30">
         <v>42</v>
       </c>
@@ -23138,7 +23134,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="30">
         <v>52</v>
       </c>
@@ -23173,7 +23169,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="30">
         <v>69</v>
       </c>
@@ -23208,7 +23204,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>21</v>
       </c>
@@ -23243,7 +23239,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>45</v>
       </c>
@@ -23278,7 +23274,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>50</v>
       </c>
@@ -23313,7 +23309,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>30</v>
       </c>
@@ -23348,7 +23344,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>70</v>
       </c>
@@ -23383,7 +23379,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>35</v>
       </c>
@@ -23418,7 +23414,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="30">
         <v>28</v>
       </c>
@@ -23453,7 +23449,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="30">
         <v>31</v>
       </c>
@@ -23488,7 +23484,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="30">
         <v>40</v>
       </c>
@@ -23523,7 +23519,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="30">
         <v>66</v>
       </c>
@@ -23558,7 +23554,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="30">
         <v>67</v>
       </c>
@@ -23593,7 +23589,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="30">
         <v>24</v>
       </c>
@@ -23628,7 +23624,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>25</v>
       </c>
@@ -23663,7 +23659,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>39</v>
       </c>
@@ -23698,7 +23694,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>38</v>
       </c>
@@ -23741,22 +23737,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08FFB760-E84D-49E7-B8A4-495A419EC16F}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -23791,7 +23787,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="30">
         <v>75</v>
       </c>
@@ -23826,7 +23822,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>11</v>
       </c>
@@ -23861,7 +23857,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>17</v>
       </c>
@@ -23896,7 +23892,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>98</v>
       </c>
@@ -23931,7 +23927,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>72</v>
       </c>
@@ -23966,7 +23962,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>15</v>
       </c>
@@ -24001,7 +23997,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -24036,7 +24032,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -24071,7 +24067,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>96</v>
       </c>
@@ -24106,7 +24102,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -24141,7 +24137,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>20</v>
       </c>
@@ -24176,7 +24172,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>76</v>
       </c>
@@ -24211,7 +24207,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
         <v>79</v>
       </c>
@@ -24246,7 +24242,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>80</v>
       </c>
@@ -24281,7 +24277,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
         <v>85</v>
       </c>
@@ -24316,7 +24312,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>12</v>
       </c>
@@ -24351,7 +24347,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>16</v>
       </c>
@@ -24386,7 +24382,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="30">
         <v>18</v>
       </c>
@@ -24421,7 +24417,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>77</v>
       </c>
@@ -24456,7 +24452,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>99</v>
       </c>
@@ -24491,7 +24487,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>19</v>
       </c>
@@ -24526,7 +24522,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>41</v>
       </c>
@@ -24561,7 +24557,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>73</v>
       </c>
@@ -24596,7 +24592,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>74</v>
       </c>
@@ -24631,7 +24627,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="30">
         <v>82</v>
       </c>
@@ -24666,7 +24662,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>83</v>
       </c>
@@ -24701,7 +24697,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="30">
         <v>84</v>
       </c>
@@ -24736,7 +24732,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="30">
         <v>88</v>
       </c>
@@ -24771,7 +24767,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
         <v>90</v>
       </c>
@@ -24806,7 +24802,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>93</v>
       </c>
@@ -24841,7 +24837,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>95</v>
       </c>
@@ -24876,7 +24872,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>7</v>
       </c>
@@ -24911,7 +24907,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>13</v>
       </c>
@@ -24946,7 +24942,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>78</v>
       </c>
@@ -24981,7 +24977,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>81</v>
       </c>
@@ -25016,7 +25012,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="34">
         <v>86</v>
       </c>
@@ -25051,7 +25047,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="30">
         <v>87</v>
       </c>
@@ -25086,7 +25082,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="30">
         <v>89</v>
       </c>
@@ -25121,7 +25117,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="30">
         <v>94</v>
       </c>
@@ -25156,7 +25152,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="30">
         <v>1</v>
       </c>
@@ -25191,7 +25187,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>2</v>
       </c>
@@ -25226,7 +25222,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>3</v>
       </c>
@@ -25261,7 +25257,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>8</v>
       </c>
@@ -25296,7 +25292,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>92</v>
       </c>
@@ -25331,7 +25327,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>97</v>
       </c>
@@ -25366,7 +25362,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>10</v>
       </c>
@@ -25401,7 +25397,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>14</v>
       </c>
@@ -25436,7 +25432,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="30">
         <v>91</v>
       </c>
@@ -25471,7 +25467,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="30">
         <v>100</v>
       </c>
@@ -25506,7 +25502,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="30">
         <v>9</v>
       </c>
@@ -25541,7 +25537,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="20">
         <v>36</v>
       </c>
@@ -25576,7 +25572,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>32</v>
       </c>
@@ -25611,7 +25607,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>54</v>
       </c>
@@ -25646,7 +25642,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>29</v>
       </c>
@@ -25681,7 +25677,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>26</v>
       </c>
@@ -25716,7 +25712,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>27</v>
       </c>
@@ -25751,7 +25747,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="30">
         <v>48</v>
       </c>
@@ -25786,7 +25782,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="30">
         <v>53</v>
       </c>
@@ -25821,7 +25817,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="30">
         <v>58</v>
       </c>
@@ -25856,7 +25852,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="30">
         <v>62</v>
       </c>
@@ -25891,7 +25887,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="30">
         <v>63</v>
       </c>
@@ -25926,7 +25922,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="30">
         <v>68</v>
       </c>
@@ -25961,7 +25957,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>33</v>
       </c>
@@ -25996,7 +25992,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>37</v>
       </c>
@@ -26031,7 +26027,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>59</v>
       </c>
@@ -26066,7 +26062,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>22</v>
       </c>
@@ -26101,7 +26097,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>23</v>
       </c>
@@ -26136,7 +26132,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>56</v>
       </c>
@@ -26171,7 +26167,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="30">
         <v>55</v>
       </c>
@@ -26206,7 +26202,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="30">
         <v>57</v>
       </c>
@@ -26241,7 +26237,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="30">
         <v>60</v>
       </c>
@@ -26276,7 +26272,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="30">
         <v>61</v>
       </c>
@@ -26311,7 +26307,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="30">
         <v>64</v>
       </c>
@@ -26346,7 +26342,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>65</v>
       </c>
@@ -26381,7 +26377,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>43</v>
       </c>
@@ -26416,7 +26412,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>44</v>
       </c>
@@ -26451,7 +26447,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>46</v>
       </c>
@@ -26486,7 +26482,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>49</v>
       </c>
@@ -26521,7 +26517,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>51</v>
       </c>
@@ -26556,7 +26552,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="30">
         <v>71</v>
       </c>
@@ -26591,7 +26587,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="30">
         <v>47</v>
       </c>
@@ -26626,7 +26622,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="30">
         <v>34</v>
       </c>
@@ -26661,7 +26657,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="30">
         <v>42</v>
       </c>
@@ -26696,7 +26692,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="30">
         <v>52</v>
       </c>
@@ -26731,7 +26727,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="30">
         <v>69</v>
       </c>
@@ -26766,7 +26762,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>21</v>
       </c>
@@ -26801,7 +26797,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>45</v>
       </c>
@@ -26836,7 +26832,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>50</v>
       </c>
@@ -26871,7 +26867,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>30</v>
       </c>
@@ -26906,7 +26902,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>70</v>
       </c>
@@ -26941,7 +26937,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>35</v>
       </c>
@@ -26976,7 +26972,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="30">
         <v>28</v>
       </c>
@@ -27011,7 +27007,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="30">
         <v>31</v>
       </c>
@@ -27046,7 +27042,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="30">
         <v>40</v>
       </c>
@@ -27081,7 +27077,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="30">
         <v>66</v>
       </c>
@@ -27116,7 +27112,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="30">
         <v>67</v>
       </c>
@@ -27151,7 +27147,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="30">
         <v>24</v>
       </c>
@@ -27186,7 +27182,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>25</v>
       </c>
@@ -27221,7 +27217,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>39</v>
       </c>
@@ -27256,7 +27252,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>38</v>
       </c>

--- a/goldStandard/_Assessment.xlsx
+++ b/goldStandard/_Assessment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55FD164-E9C3-4F72-96B8-A3A10797309D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EBEAB2-2AC5-47AF-A9C3-A62F36BDB223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="19365" windowHeight="15240" xr2:uid="{47C0CA8E-5BD4-46FF-B103-6FF28F611458}"/>
+    <workbookView xWindow="420" yWindow="0" windowWidth="21195" windowHeight="20985" xr2:uid="{47C0CA8E-5BD4-46FF-B103-6FF28F611458}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="170">
   <si>
     <t>Number</t>
   </si>
@@ -442,9 +442,6 @@
     <t>Quantile;VSN;CyclicLoess</t>
   </si>
   <si>
-    <t>Median;Log</t>
-  </si>
-  <si>
     <t>CyclicLoess;RLR</t>
   </si>
   <si>
@@ -521,9 +518,6 @@
     <t>Log;Median;Mean;TI</t>
   </si>
   <si>
-    <t>RLR;CyclicLoess</t>
-  </si>
-  <si>
     <t>Mean;TI;Log;Median</t>
   </si>
   <si>
@@ -546,6 +540,12 @@
   </si>
   <si>
     <t>Mean;CyclicLoess</t>
+  </si>
+  <si>
+    <t>Median;VSN;Quantile</t>
+  </si>
+  <si>
+    <t>Quantile;Log</t>
   </si>
 </sst>
 </file>
@@ -1212,13 +1212,13 @@
         <v>102</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>103</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>109</v>
@@ -1240,7 +1240,7 @@
       <c r="A2" s="2"/>
       <c r="B2" s="17"/>
       <c r="C2" s="42" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>104</v>
@@ -1305,7 +1305,7 @@
         <v>Quantile</v>
       </c>
       <c r="J3" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K3" s="24" t="s">
         <v>112</v>
@@ -1455,7 +1455,7 @@
         <v>Quantile</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K6" s="30"/>
       <c r="L6" s="26">
@@ -1506,7 +1506,7 @@
         <v>116</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L7" s="26">
         <v>1</v>
@@ -1603,7 +1603,7 @@
         <v>Median</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="8">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E10" t="str">
         <f>Item2!K9</f>
-        <v>CyclicLoess</v>
+        <v>Log</v>
       </c>
       <c r="F10" t="str">
         <f>Item3!K9</f>
@@ -1748,7 +1748,7 @@
         <v>Quantile</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>112</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E15" s="27" t="str">
         <f>Item2!K14</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="F15" s="27" t="str">
         <f>Item3!K14</f>
@@ -1942,7 +1942,7 @@
         <v>Quantile</v>
       </c>
       <c r="J16" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K16" s="30" t="s">
         <v>112</v>
@@ -1989,10 +1989,10 @@
         <v>Quantile</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K17" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L17" s="26">
         <v>3</v>
@@ -2036,7 +2036,7 @@
         <v>Median</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K18" s="30" t="s">
         <v>131</v>
@@ -2083,10 +2083,10 @@
         <v>Quantile</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L19" s="26">
         <v>3</v>
@@ -2180,7 +2180,7 @@
         <v>130</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L21" s="8">
         <v>4</v>
@@ -2269,7 +2269,7 @@
         <v>Quantile</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>112</v>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="E24" t="str">
         <f>Item2!K23</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="F24" t="str">
         <f>Item3!K23</f>
@@ -2319,7 +2319,7 @@
         <v>116</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L24" s="8">
         <v>4</v>
@@ -2363,7 +2363,7 @@
         <v>CyclicLoess</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>112</v>
@@ -2413,7 +2413,7 @@
         <v>116</v>
       </c>
       <c r="K26" s="30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L26" s="26">
         <v>5</v>
@@ -2831,10 +2831,10 @@
         <v>RLR</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L35" s="8">
         <v>6</v>
@@ -3019,10 +3019,10 @@
         <v>Quantile</v>
       </c>
       <c r="J39" s="26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K39" s="30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L39" s="26">
         <v>7</v>
@@ -3113,10 +3113,10 @@
         <v>Median</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K41" s="30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L41" s="26">
         <v>7</v>
@@ -3160,7 +3160,7 @@
         <v>Quantile</v>
       </c>
       <c r="J42" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K42" s="30" t="s">
         <v>112</v>
@@ -3254,7 +3254,7 @@
         <v>Quantile</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>112</v>
@@ -3393,7 +3393,7 @@
         <v>Quantile</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="8">
@@ -3483,10 +3483,10 @@
         <v>Quantile</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L49" s="8">
         <v>8</v>
@@ -3530,7 +3530,7 @@
         <v>Quantile</v>
       </c>
       <c r="J50" s="26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K50" s="30" t="s">
         <v>112</v>
@@ -3625,7 +3625,7 @@
         <v>116</v>
       </c>
       <c r="K52" s="30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L52" s="26">
         <v>9</v>
@@ -3669,7 +3669,7 @@
         <v>Quantile</v>
       </c>
       <c r="J53" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K53" s="21" t="s">
         <v>131</v>
@@ -3716,7 +3716,7 @@
         <v>Quantile</v>
       </c>
       <c r="J54" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K54" s="8" t="s">
         <v>131</v>
@@ -3766,7 +3766,7 @@
         <v>132</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L55">
         <v>1</v>
@@ -3870,7 +3870,7 @@
         <v>27</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
         <v>123</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="D61" s="30" t="str">
         <f>Item1!K60</f>
-        <v>VSN</v>
+        <v>Log</v>
       </c>
       <c r="E61" s="27" t="str">
         <f>Item2!K60</f>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="F61" s="27" t="str">
         <f>Item3!K60</f>
-        <v>VSN</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="G61" s="27" t="str">
         <f>Item4!K60</f>
@@ -4030,18 +4030,16 @@
       </c>
       <c r="H61" s="27" t="str">
         <f>Item5!K60</f>
-        <v>VSN</v>
+        <v>Quantile</v>
       </c>
       <c r="I61" s="28" t="str">
         <f>Item6!K60</f>
-        <v>VSN</v>
+        <v>Quantile</v>
       </c>
       <c r="J61" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="K61" s="26" t="s">
-        <v>161</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="K61" s="26"/>
       <c r="L61" s="27">
         <v>2</v>
       </c>
@@ -4129,7 +4127,7 @@
         <v>Quantile</v>
       </c>
       <c r="J63" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K63" s="26" t="s">
         <v>131</v>
@@ -4375,7 +4373,7 @@
         <v>23</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C69" t="s">
         <v>123</v>
@@ -4683,7 +4681,7 @@
         <v>Quantile</v>
       </c>
       <c r="J75" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K75" s="8"/>
       <c r="L75" s="27">
@@ -4728,10 +4726,10 @@
         <v>Quantile</v>
       </c>
       <c r="J76" t="s">
+        <v>168</v>
+      </c>
+      <c r="K76" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="K76" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="L76">
         <v>5</v>
@@ -4778,7 +4776,7 @@
         <v>117</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L77">
         <v>5</v>
@@ -4822,7 +4820,7 @@
         <v>Quantile</v>
       </c>
       <c r="J78" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K78" s="8" t="s">
         <v>131</v>
@@ -4919,7 +4917,7 @@
         <v>132</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L80">
         <v>5</v>
@@ -4966,7 +4964,7 @@
         <v>116</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L81">
         <v>5</v>
@@ -5100,7 +5098,7 @@
         <v>Quantile</v>
       </c>
       <c r="J84" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K84" s="26"/>
       <c r="L84" s="27">
@@ -5190,10 +5188,10 @@
         <v>Quantile</v>
       </c>
       <c r="J86" s="27" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K86" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L86" s="27">
         <v>6</v>
@@ -5218,7 +5216,7 @@
       </c>
       <c r="E87" s="27" t="str">
         <f>Item2!K86</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="F87" s="27" t="str">
         <f>Item3!K86</f>
@@ -5284,7 +5282,7 @@
         <v>Median</v>
       </c>
       <c r="J88" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K88" s="8"/>
       <c r="L88">
@@ -5331,9 +5329,7 @@
       <c r="J89" t="s">
         <v>133</v>
       </c>
-      <c r="K89" s="8" t="s">
-        <v>112</v>
-      </c>
+      <c r="K89" s="8"/>
       <c r="L89">
         <v>7</v>
       </c>
@@ -5468,9 +5464,7 @@
       <c r="J92" t="s">
         <v>114</v>
       </c>
-      <c r="K92" s="8" t="s">
-        <v>158</v>
-      </c>
+      <c r="K92" s="8"/>
       <c r="L92">
         <v>7</v>
       </c>
@@ -5494,7 +5488,7 @@
       </c>
       <c r="E93" t="str">
         <f>Item2!K92</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="F93" t="str">
         <f>Item3!K92</f>
@@ -5648,7 +5642,7 @@
         <v>Quantile</v>
       </c>
       <c r="J96" s="27" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K96" s="26" t="s">
         <v>132</v>
@@ -5742,7 +5736,7 @@
         <v>Quantile</v>
       </c>
       <c r="J98" s="27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K98" s="26"/>
       <c r="L98" s="27">
@@ -5880,7 +5874,7 @@
         <v>132</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L101">
         <v>9</v>
@@ -5940,6 +5934,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7926,7 +7921,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" s="3">
         <v>6</v>
@@ -8034,16 +8029,16 @@
         <v>57</v>
       </c>
       <c r="C60" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" s="27">
         <v>3</v>
@@ -8052,13 +8047,13 @@
         <v>5</v>
       </c>
       <c r="I60" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" s="28">
         <v>4</v>
       </c>
       <c r="K60" s="28" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -8311,7 +8306,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C68" s="3">
         <v>6</v>
@@ -9807,31 +9802,31 @@
         <v>7</v>
       </c>
       <c r="C9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -9982,31 +9977,31 @@
         <v>78</v>
       </c>
       <c r="C14" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="28" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -10297,31 +10292,31 @@
         <v>40</v>
       </c>
       <c r="C23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -11484,7 +11479,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" s="3">
         <v>2</v>
@@ -11869,7 +11864,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C68" s="3">
         <v>2</v>
@@ -12502,31 +12497,31 @@
         <v>68</v>
       </c>
       <c r="C86" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K86" s="28" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -12712,31 +12707,31 @@
         <v>34</v>
       </c>
       <c r="C92" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -15042,7 +15037,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" s="3">
         <v>3</v>
@@ -15165,16 +15160,16 @@
         <v>4</v>
       </c>
       <c r="H60" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" s="28">
         <v>5</v>
       </c>
       <c r="K60" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -15401,7 +15396,7 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -15410,7 +15405,7 @@
         <v>1</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I67">
         <v>2</v>
@@ -15427,7 +15422,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C68" s="3">
         <v>3</v>
@@ -18601,7 +18596,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" s="3">
         <v>3</v>
@@ -18986,7 +18981,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C68" s="3">
         <v>3</v>
@@ -22159,7 +22154,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" s="3">
         <v>1</v>
@@ -22270,28 +22265,28 @@
         <v>2</v>
       </c>
       <c r="D60" s="27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E60" s="27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F60" s="27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G60" s="27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H60" s="27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I60" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J60" s="28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K60" s="28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -22544,7 +22539,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -25717,7 +25712,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" s="3">
         <v>3</v>
@@ -25825,7 +25820,7 @@
         <v>57</v>
       </c>
       <c r="C60" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" s="27">
         <v>2</v>
@@ -25837,19 +25832,19 @@
         <v>2</v>
       </c>
       <c r="G60" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H60" s="27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I60" s="27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J60" s="28">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K60" s="28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -26102,7 +26097,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C68" s="3">
         <v>3</v>

--- a/goldStandard/_Assessment.xlsx
+++ b/goldStandard/_Assessment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Documents\GitHub\normScore-development\goldStandard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76F55E6-61C8-4A9A-A19D-1D7277CA311F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D6BEF1-D6DD-4264-BD6D-92F503DE90EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="1125" windowWidth="20685" windowHeight="19155" xr2:uid="{47C0CA8E-5BD4-46FF-B103-6FF28F611458}"/>
+    <workbookView xWindow="1590" yWindow="1215" windowWidth="15240" windowHeight="19365" activeTab="2" xr2:uid="{47C0CA8E-5BD4-46FF-B103-6FF28F611458}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,12 @@
     <sheet name="Item4" sheetId="5" r:id="rId5"/>
     <sheet name="Item5" sheetId="6" r:id="rId6"/>
     <sheet name="Item6" sheetId="7" r:id="rId7"/>
+    <sheet name="Old_Item5" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Item4!$A$1:$K$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Item5!$A$1:$K$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Old_Item5!$A$1:$K$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="167">
   <si>
     <t>Number</t>
   </si>
@@ -448,9 +450,6 @@
     <t>Log;Median</t>
   </si>
   <si>
-    <t>Log;Quantile;Median</t>
-  </si>
-  <si>
     <t>Quantile;Median</t>
   </si>
   <si>
@@ -521,22 +520,10 @@
     <t>Quantile;Median;CyclicLoess</t>
   </si>
   <si>
-    <t>CyclicLoess;Median</t>
-  </si>
-  <si>
     <t>Quantile;VSN</t>
   </si>
   <si>
-    <t>Log;CyclicLoess;Quantile</t>
-  </si>
-  <si>
-    <t>Quantile;VSN;CyclicLoess;RLR</t>
-  </si>
-  <si>
     <t>Log;VSN</t>
-  </si>
-  <si>
-    <t>Mean;CyclicLoess</t>
   </si>
   <si>
     <t>Median;VSN;Quantile</t>
@@ -549,6 +536,9 @@
   </si>
   <si>
     <t>Quantile;RLR</t>
+  </si>
+  <si>
+    <t>Quantile;CyclicLoess;RLR;VSN</t>
   </si>
 </sst>
 </file>
@@ -789,7 +779,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -861,6 +851,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1215,13 +1207,13 @@
         <v>101</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>102</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>108</v>
@@ -1243,7 +1235,7 @@
       <c r="A2" s="2"/>
       <c r="B2" s="17"/>
       <c r="C2" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>103</v>
@@ -1301,14 +1293,14 @@
       </c>
       <c r="H3" s="31" t="str">
         <f>Item5!K2</f>
-        <v>Log</v>
+        <v>Quantile</v>
       </c>
       <c r="I3" s="29" t="str">
         <f>Item6!K2</f>
         <v>Quantile</v>
       </c>
       <c r="J3" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K3" s="24" t="s">
         <v>111</v>
@@ -1351,7 +1343,7 @@
       </c>
       <c r="H4" s="27" t="str">
         <f>Item5!K3</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I4" s="28" t="str">
         <f>Item6!K3</f>
@@ -1389,7 +1381,7 @@
       </c>
       <c r="E5" s="27" t="str">
         <f>Item2!K4</f>
-        <v>Log</v>
+        <v>Quantile</v>
       </c>
       <c r="F5" s="27" t="str">
         <f>Item3!K4</f>
@@ -1401,7 +1393,7 @@
       </c>
       <c r="H5" s="27" t="str">
         <f>Item5!K4</f>
-        <v>Median</v>
+        <v>Quantile</v>
       </c>
       <c r="I5" s="28" t="str">
         <f>Item6!K4</f>
@@ -1439,7 +1431,7 @@
       </c>
       <c r="E6" s="27" t="str">
         <f>Item2!K5</f>
-        <v>CyclicLoess</v>
+        <v>Log</v>
       </c>
       <c r="F6" s="27" t="str">
         <f>Item3!K5</f>
@@ -1451,14 +1443,14 @@
       </c>
       <c r="H6" s="27" t="str">
         <f>Item5!K5</f>
-        <v>Quantile</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I6" s="28" t="str">
         <f>Item6!K5</f>
         <v>Quantile</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K6" s="30"/>
       <c r="L6" s="26">
@@ -1499,7 +1491,7 @@
       </c>
       <c r="H7" s="27" t="str">
         <f>Item5!K6</f>
-        <v>Quantile</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I7" s="28" t="str">
         <f>Item6!K6</f>
@@ -1509,7 +1501,7 @@
         <v>115</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L7" s="26">
         <v>1</v>
@@ -1599,14 +1591,14 @@
       </c>
       <c r="H9" t="str">
         <f>Item5!K8</f>
-        <v>Log</v>
+        <v>Median</v>
       </c>
       <c r="I9" s="4" t="str">
         <f>Item6!K8</f>
         <v>Median</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="8">
@@ -1647,7 +1639,7 @@
       </c>
       <c r="H10" t="str">
         <f>Item5!K9</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I10" s="4" t="str">
         <f>Item6!K9</f>
@@ -1694,7 +1686,7 @@
       </c>
       <c r="H11" t="str">
         <f>Item5!K10</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I11" s="4" t="str">
         <f>Item6!K10</f>
@@ -1744,14 +1736,14 @@
       </c>
       <c r="H12" t="str">
         <f>Item5!K11</f>
-        <v>Median</v>
+        <v>Quantile</v>
       </c>
       <c r="I12" s="4" t="str">
         <f>Item6!K11</f>
         <v>Quantile</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>111</v>
@@ -1794,7 +1786,7 @@
       </c>
       <c r="H13" t="str">
         <f>Item5!K12</f>
-        <v>Median</v>
+        <v>Quantile</v>
       </c>
       <c r="I13" s="4" t="str">
         <f>Item6!K12</f>
@@ -1844,7 +1836,7 @@
       </c>
       <c r="H14" t="str">
         <f>Item5!K13</f>
-        <v>Log</v>
+        <v>Quantile</v>
       </c>
       <c r="I14" s="4" t="str">
         <f>Item6!K13</f>
@@ -1891,7 +1883,7 @@
       </c>
       <c r="H15" s="27" t="str">
         <f>Item5!K14</f>
-        <v>Mean</v>
+        <v>Median</v>
       </c>
       <c r="I15" s="28" t="str">
         <f>Item6!K14</f>
@@ -1938,14 +1930,14 @@
       </c>
       <c r="H16" s="27" t="str">
         <f>Item5!K15</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I16" s="28" t="str">
         <f>Item6!K15</f>
         <v>Quantile</v>
       </c>
       <c r="J16" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K16" s="30" t="s">
         <v>111</v>
@@ -1992,10 +1984,10 @@
         <v>Quantile</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K17" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L17" s="26">
         <v>3</v>
@@ -2032,14 +2024,14 @@
       </c>
       <c r="H18" s="27" t="str">
         <f>Item5!K17</f>
-        <v>Median</v>
+        <v>Quantile</v>
       </c>
       <c r="I18" s="28" t="str">
         <f>Item6!K17</f>
         <v>Median</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K18" s="30" t="s">
         <v>130</v>
@@ -2079,17 +2071,17 @@
       </c>
       <c r="H19" s="27" t="str">
         <f>Item5!K18</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I19" s="28" t="str">
         <f>Item6!K18</f>
         <v>Quantile</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L19" s="26">
         <v>3</v>
@@ -2126,7 +2118,7 @@
       </c>
       <c r="H20" s="27" t="str">
         <f>Item5!K19</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I20" s="28" t="str">
         <f>Item6!K19</f>
@@ -2173,7 +2165,7 @@
       </c>
       <c r="H21" t="str">
         <f>Item5!K20</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I21" s="4" t="str">
         <f>Item6!K20</f>
@@ -2183,7 +2175,7 @@
         <v>129</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L21" s="8">
         <v>4</v>
@@ -2220,7 +2212,7 @@
       </c>
       <c r="H22" t="str">
         <f>Item5!K21</f>
-        <v>Log</v>
+        <v>RLR</v>
       </c>
       <c r="I22" s="4" t="str">
         <f>Item6!K21</f>
@@ -2265,7 +2257,7 @@
       </c>
       <c r="H23" t="str">
         <f>Item5!K22</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I23" s="4" t="str">
         <f>Item6!K22</f>
@@ -2312,7 +2304,7 @@
       </c>
       <c r="H24" t="str">
         <f>Item5!K23</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I24" s="4" t="str">
         <f>Item6!K23</f>
@@ -2322,7 +2314,7 @@
         <v>115</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L24" s="8">
         <v>4</v>
@@ -2406,7 +2398,7 @@
       </c>
       <c r="H26" s="27" t="str">
         <f>Item5!K25</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I26" s="28" t="str">
         <f>Item6!K25</f>
@@ -2453,7 +2445,7 @@
       </c>
       <c r="H27" s="27" t="str">
         <f>Item5!K26</f>
-        <v>TI</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I27" s="28" t="str">
         <f>Item6!K26</f>
@@ -2473,47 +2465,47 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+      <c r="A28" s="30">
         <v>83</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="D28" t="str">
+      <c r="D28" s="27" t="str">
         <f>Item1!K27</f>
         <v>Log</v>
       </c>
-      <c r="E28" t="str">
+      <c r="E28" s="27" t="str">
         <f>Item2!K27</f>
         <v>CyclicLoess</v>
       </c>
-      <c r="F28" t="str">
+      <c r="F28" s="27" t="str">
         <f>Item3!K27</f>
         <v>Median</v>
       </c>
-      <c r="G28" t="str">
+      <c r="G28" s="27" t="str">
         <f>Item4!K27</f>
         <v>Log</v>
       </c>
-      <c r="H28" t="str">
+      <c r="H28" s="27" t="str">
         <f>Item5!K27</f>
-        <v>Median</v>
-      </c>
-      <c r="I28" s="4" t="str">
+        <v>Quantile</v>
+      </c>
+      <c r="I28" s="28" t="str">
         <f>Item6!K27</f>
         <v>Log</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="8">
-        <v>5</v>
-      </c>
-      <c r="M28" s="4">
+      <c r="K28" s="30"/>
+      <c r="L28" s="26">
+        <v>5</v>
+      </c>
+      <c r="M28" s="28">
         <v>3</v>
       </c>
     </row>
@@ -2545,7 +2537,7 @@
       </c>
       <c r="H29" s="27" t="str">
         <f>Item5!K28</f>
-        <v>Log</v>
+        <v>Median</v>
       </c>
       <c r="I29" s="28" t="str">
         <f>Item6!K28</f>
@@ -2686,7 +2678,7 @@
       </c>
       <c r="H32" t="str">
         <f>Item5!K31</f>
-        <v>Median</v>
+        <v>Quantile</v>
       </c>
       <c r="I32" s="4" t="str">
         <f>Item6!K31</f>
@@ -2837,7 +2829,7 @@
         <v>134</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L35" s="8">
         <v>6</v>
@@ -2874,7 +2866,7 @@
       </c>
       <c r="H36" t="str">
         <f>Item5!K35</f>
-        <v>Log</v>
+        <v>Median</v>
       </c>
       <c r="I36" s="4" t="str">
         <f>Item6!K35</f>
@@ -2968,17 +2960,17 @@
       </c>
       <c r="H38" s="27" t="str">
         <f>Item5!K37</f>
-        <v>Quantile</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I38" s="28" t="str">
         <f>Item6!K37</f>
         <v>Quantile</v>
       </c>
       <c r="J38" s="26" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="K38" s="30" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="L38" s="26">
         <v>7</v>
@@ -2999,7 +2991,7 @@
       </c>
       <c r="D39" s="27" t="str">
         <f>Item1!K38</f>
-        <v>CyclicLoess</v>
+        <v>Median</v>
       </c>
       <c r="E39" s="27" t="str">
         <f>Item2!K38</f>
@@ -3015,17 +3007,17 @@
       </c>
       <c r="H39" s="27" t="str">
         <f>Item5!K38</f>
-        <v>CyclicLoess</v>
+        <v>Median</v>
       </c>
       <c r="I39" s="28" t="str">
         <f>Item6!K38</f>
         <v>Quantile</v>
       </c>
       <c r="J39" s="26" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="K39" s="30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L39" s="26">
         <v>7</v>
@@ -3116,10 +3108,10 @@
         <v>Median</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K41" s="30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L41" s="26">
         <v>7</v>
@@ -3156,14 +3148,14 @@
       </c>
       <c r="H42" s="27" t="str">
         <f>Item5!K41</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I42" s="28" t="str">
         <f>Item6!K41</f>
         <v>Quantile</v>
       </c>
       <c r="J42" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K42" s="30" t="s">
         <v>111</v>
@@ -3180,7 +3172,7 @@
         <v>2</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C43" s="26" t="s">
         <v>121</v>
@@ -3203,14 +3195,14 @@
       </c>
       <c r="H43" s="27" t="str">
         <f>Item5!K42</f>
-        <v>Quantile</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I43" s="28" t="str">
         <f>Item6!K42</f>
         <v>Quantile</v>
       </c>
       <c r="J43" s="26" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="K43" s="30" t="s">
         <v>111</v>
@@ -3257,7 +3249,7 @@
         <v>Quantile</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>111</v>
@@ -3297,16 +3289,18 @@
       </c>
       <c r="H45" t="str">
         <f>Item5!K44</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I45" s="4" t="str">
         <f>Item6!K44</f>
         <v>Quantile</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="K45" s="3"/>
+        <v>129</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="L45" s="8">
         <v>8</v>
       </c>
@@ -3342,14 +3336,14 @@
       </c>
       <c r="H46" t="str">
         <f>Item5!K45</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I46" s="4" t="str">
         <f>Item6!K45</f>
         <v>Quantile</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>111</v>
@@ -3389,14 +3383,14 @@
       </c>
       <c r="H47" t="str">
         <f>Item5!K46</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I47" s="4" t="str">
         <f>Item6!K46</f>
         <v>Quantile</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="8">
@@ -3434,14 +3428,14 @@
       </c>
       <c r="H48" t="str">
         <f>Item5!K47</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I48" s="4" t="str">
         <f>Item6!K47</f>
         <v>Quantile</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="8">
@@ -3479,17 +3473,17 @@
       </c>
       <c r="H49" t="str">
         <f>Item5!K48</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I49" s="4" t="str">
         <f>Item6!K48</f>
         <v>Quantile</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L49" s="8">
         <v>8</v>
@@ -3533,7 +3527,7 @@
         <v>Quantile</v>
       </c>
       <c r="J50" s="26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K50" s="30" t="s">
         <v>111</v>
@@ -3573,14 +3567,14 @@
       </c>
       <c r="H51" s="27" t="str">
         <f>Item5!K50</f>
-        <v>Log</v>
+        <v>Median</v>
       </c>
       <c r="I51" s="28" t="str">
         <f>Item6!K50</f>
         <v>Quantile</v>
       </c>
       <c r="J51" s="26" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K51" s="30"/>
       <c r="L51" s="26">
@@ -3618,17 +3612,17 @@
       </c>
       <c r="H52" s="27" t="str">
         <f>Item5!K51</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I52" s="28" t="str">
         <f>Item6!K51</f>
         <v>Quantile</v>
       </c>
-      <c r="J52" s="26" t="s">
-        <v>115</v>
+      <c r="J52" s="44" t="s">
+        <v>129</v>
       </c>
       <c r="K52" s="30" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L52" s="26">
         <v>9</v>
@@ -3665,14 +3659,14 @@
       </c>
       <c r="H53" s="23" t="str">
         <f>Item5!K52</f>
-        <v>Median</v>
+        <v>Log</v>
       </c>
       <c r="I53" s="33" t="str">
         <f>Item6!K52</f>
         <v>Quantile</v>
       </c>
       <c r="J53" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K53" s="21" t="s">
         <v>130</v>
@@ -3712,14 +3706,14 @@
       </c>
       <c r="H54" t="str">
         <f>Item5!K53</f>
-        <v>Median</v>
+        <v>Log</v>
       </c>
       <c r="I54" s="4" t="str">
         <f>Item6!K53</f>
         <v>Quantile</v>
       </c>
       <c r="J54" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K54" s="8" t="s">
         <v>130</v>
@@ -3769,7 +3763,7 @@
         <v>131</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L55">
         <v>1</v>
@@ -3806,7 +3800,7 @@
       </c>
       <c r="H56" t="str">
         <f>Item5!K55</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I56" s="4" t="str">
         <f>Item6!K55</f>
@@ -3851,14 +3845,14 @@
       </c>
       <c r="H57" t="str">
         <f>Item5!K56</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I57" s="4" t="str">
         <f>Item6!K56</f>
         <v>Quantile</v>
       </c>
       <c r="J57" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="K57" s="8"/>
       <c r="L57">
@@ -3873,7 +3867,7 @@
         <v>27</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C58" t="s">
         <v>122</v>
@@ -3896,7 +3890,7 @@
       </c>
       <c r="H58" t="str">
         <f>Item5!K57</f>
-        <v>Log</v>
+        <v>Quantile</v>
       </c>
       <c r="I58" s="4" t="str">
         <f>Item6!K57</f>
@@ -3941,7 +3935,7 @@
       </c>
       <c r="H59" s="27" t="str">
         <f>Item5!K58</f>
-        <v>Median</v>
+        <v>Quantile</v>
       </c>
       <c r="I59" s="28" t="str">
         <f>Item6!K58</f>
@@ -3988,14 +3982,14 @@
       </c>
       <c r="H60" s="27" t="str">
         <f>Item5!K59</f>
-        <v>Log</v>
+        <v>Median</v>
       </c>
       <c r="I60" s="28" t="str">
         <f>Item6!K59</f>
         <v>Quantile</v>
       </c>
       <c r="J60" s="27" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="K60" s="26"/>
       <c r="L60" s="27">
@@ -4033,14 +4027,14 @@
       </c>
       <c r="H61" s="27" t="str">
         <f>Item5!K60</f>
-        <v>Quantile</v>
+        <v>Log</v>
       </c>
       <c r="I61" s="28" t="str">
         <f>Item6!K60</f>
         <v>Quantile</v>
       </c>
       <c r="J61" s="27" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K61" s="26"/>
       <c r="L61" s="27">
@@ -4123,14 +4117,14 @@
       </c>
       <c r="H63" s="27" t="str">
         <f>Item5!K62</f>
-        <v>Log</v>
+        <v>Quantile</v>
       </c>
       <c r="I63" s="28" t="str">
         <f>Item6!K62</f>
         <v>Quantile</v>
       </c>
       <c r="J63" s="27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K63" s="26" t="s">
         <v>130</v>
@@ -4217,7 +4211,7 @@
       </c>
       <c r="H65" t="str">
         <f>Item5!K64</f>
-        <v>Log</v>
+        <v>Median</v>
       </c>
       <c r="I65" s="4" t="str">
         <f>Item6!K64</f>
@@ -4264,14 +4258,14 @@
       </c>
       <c r="H66" t="str">
         <f>Item5!K65</f>
-        <v>Median</v>
+        <v>Quantile</v>
       </c>
       <c r="I66" s="4" t="str">
         <f>Item6!K65</f>
         <v>Log</v>
       </c>
       <c r="J66" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="K66" s="8"/>
       <c r="L66">
@@ -4309,14 +4303,14 @@
       </c>
       <c r="H67" t="str">
         <f>Item5!K66</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I67" s="4" t="str">
         <f>Item6!K66</f>
         <v>Quantile</v>
       </c>
       <c r="J67" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K67" s="8"/>
       <c r="L67">
@@ -4354,14 +4348,14 @@
       </c>
       <c r="H68" t="str">
         <f>Item5!K67</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I68" s="4" t="str">
         <f>Item6!K67</f>
         <v>Quantile</v>
       </c>
       <c r="J68" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="K68" s="8"/>
       <c r="L68">
@@ -4376,7 +4370,7 @@
         <v>23</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C69" t="s">
         <v>122</v>
@@ -4399,7 +4393,7 @@
       </c>
       <c r="H69" t="str">
         <f>Item5!K68</f>
-        <v>Log</v>
+        <v>Median</v>
       </c>
       <c r="I69" s="4" t="str">
         <f>Item6!K68</f>
@@ -4444,14 +4438,14 @@
       </c>
       <c r="H70" t="str">
         <f>Item5!K69</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I70" s="4" t="str">
         <f>Item6!K69</f>
         <v>Quantile</v>
       </c>
       <c r="J70" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="K70" s="8" t="s">
         <v>130</v>
@@ -4491,7 +4485,7 @@
       </c>
       <c r="H71" s="27" t="str">
         <f>Item5!K70</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I71" s="28" t="str">
         <f>Item6!K70</f>
@@ -4536,7 +4530,7 @@
       </c>
       <c r="H72" s="27" t="str">
         <f>Item5!K71</f>
-        <v>Log</v>
+        <v>Median</v>
       </c>
       <c r="I72" s="28" t="str">
         <f>Item6!K71</f>
@@ -4583,7 +4577,7 @@
       </c>
       <c r="H73" s="27" t="str">
         <f>Item5!K72</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I73" s="28" t="str">
         <f>Item6!K72</f>
@@ -4630,14 +4624,14 @@
       </c>
       <c r="H74" s="27" t="str">
         <f>Item5!K73</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I74" s="28" t="str">
         <f>Item6!K73</f>
         <v>Quantile</v>
       </c>
       <c r="J74" s="27" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K74" s="26" t="s">
         <v>130</v>
@@ -4677,14 +4671,14 @@
       </c>
       <c r="H75" s="27" t="str">
         <f>Item5!K74</f>
-        <v>Log</v>
+        <v>Median</v>
       </c>
       <c r="I75" s="28" t="str">
         <f>Item6!K74</f>
         <v>Quantile</v>
       </c>
       <c r="J75" s="27" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="K75" s="8"/>
       <c r="L75" s="27">
@@ -4722,14 +4716,14 @@
       </c>
       <c r="H76" t="str">
         <f>Item5!K75</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I76" s="4" t="str">
         <f>Item6!K75</f>
         <v>Quantile</v>
       </c>
       <c r="J76" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="K76" s="8" t="s">
         <v>134</v>
@@ -4769,7 +4763,7 @@
       </c>
       <c r="H77" t="str">
         <f>Item5!K76</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I77" s="4" t="str">
         <f>Item6!K76</f>
@@ -4779,7 +4773,7 @@
         <v>116</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L77">
         <v>5</v>
@@ -4816,14 +4810,14 @@
       </c>
       <c r="H78" t="str">
         <f>Item5!K77</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I78" s="4" t="str">
         <f>Item6!K77</f>
         <v>Quantile</v>
       </c>
       <c r="J78" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="K78" s="8" t="s">
         <v>130</v>
@@ -4863,14 +4857,14 @@
       </c>
       <c r="H79" t="str">
         <f>Item5!K78</f>
-        <v>Quantile</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I79" s="4" t="str">
         <f>Item6!K78</f>
         <v>Quantile</v>
       </c>
       <c r="J79" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K79" s="8" t="s">
         <v>130</v>
@@ -4920,7 +4914,7 @@
         <v>131</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L80">
         <v>5</v>
@@ -4967,7 +4961,7 @@
         <v>115</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L81">
         <v>5</v>
@@ -4992,7 +4986,7 @@
       </c>
       <c r="E82" s="27" t="str">
         <f>Item2!K81</f>
-        <v>CyclicLoess</v>
+        <v>Log</v>
       </c>
       <c r="F82" s="27" t="str">
         <f>Item3!K81</f>
@@ -5004,7 +4998,7 @@
       </c>
       <c r="H82" s="27" t="str">
         <f>Item5!K81</f>
-        <v>Quantile</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I82" s="28" t="str">
         <f>Item6!K81</f>
@@ -5049,14 +5043,14 @@
       </c>
       <c r="H83" s="27" t="str">
         <f>Item5!K82</f>
-        <v>Log</v>
+        <v>Quantile</v>
       </c>
       <c r="I83" s="28" t="str">
         <f>Item6!K82</f>
         <v>Quantile</v>
       </c>
       <c r="J83" s="27" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K83" s="26"/>
       <c r="L83" s="27">
@@ -5094,14 +5088,14 @@
       </c>
       <c r="H84" s="27" t="str">
         <f>Item5!K83</f>
-        <v>Log</v>
+        <v>Quantile</v>
       </c>
       <c r="I84" s="28" t="str">
         <f>Item6!K83</f>
         <v>Quantile</v>
       </c>
       <c r="J84" s="27" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="K84" s="26"/>
       <c r="L84" s="27">
@@ -5139,7 +5133,7 @@
       </c>
       <c r="H85" s="27" t="str">
         <f>Item5!K84</f>
-        <v>Log</v>
+        <v>RLR</v>
       </c>
       <c r="I85" s="28" t="str">
         <f>Item6!K84</f>
@@ -5184,17 +5178,17 @@
       </c>
       <c r="H86" s="27" t="str">
         <f>Item5!K85</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I86" s="28" t="str">
         <f>Item6!K85</f>
         <v>Quantile</v>
       </c>
       <c r="J86" s="27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K86" s="26" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L86" s="27">
         <v>6</v>
@@ -5231,7 +5225,7 @@
       </c>
       <c r="H87" s="27" t="str">
         <f>Item5!K86</f>
-        <v>Log</v>
+        <v>Median</v>
       </c>
       <c r="I87" s="28" t="str">
         <f>Item6!K86</f>
@@ -5278,14 +5272,14 @@
       </c>
       <c r="H88" t="str">
         <f>Item5!K87</f>
-        <v>Median</v>
+        <v>Log</v>
       </c>
       <c r="I88" s="4" t="str">
         <f>Item6!K87</f>
         <v>Median</v>
       </c>
       <c r="J88" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K88" s="8"/>
       <c r="L88">
@@ -5368,7 +5362,7 @@
       </c>
       <c r="H90" t="str">
         <f>Item5!K89</f>
-        <v>Median</v>
+        <v>Log</v>
       </c>
       <c r="I90" s="4" t="str">
         <f>Item6!K89</f>
@@ -5413,7 +5407,7 @@
       </c>
       <c r="H91" t="str">
         <f>Item5!K90</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I91" s="4" t="str">
         <f>Item6!K90</f>
@@ -5465,7 +5459,7 @@
         <v>Quantile</v>
       </c>
       <c r="J92" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K92" s="8"/>
       <c r="L92">
@@ -5503,7 +5497,7 @@
       </c>
       <c r="H93" t="str">
         <f>Item5!K92</f>
-        <v>Median</v>
+        <v>Log</v>
       </c>
       <c r="I93" s="4" t="str">
         <f>Item6!K92</f>
@@ -5593,7 +5587,7 @@
       </c>
       <c r="H95" s="27" t="str">
         <f>Item5!K94</f>
-        <v>Log</v>
+        <v>Quantile</v>
       </c>
       <c r="I95" s="28" t="str">
         <f>Item6!K94</f>
@@ -5638,14 +5632,14 @@
       </c>
       <c r="H96" s="27" t="str">
         <f>Item5!K95</f>
-        <v>Quantile</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I96" s="28" t="str">
         <f>Item6!K95</f>
         <v>Quantile</v>
       </c>
       <c r="J96" s="27" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="K96" s="26" t="s">
         <v>131</v>
@@ -5739,7 +5733,7 @@
         <v>Quantile</v>
       </c>
       <c r="J98" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K98" s="26"/>
       <c r="L98" s="27">
@@ -5777,16 +5771,18 @@
       </c>
       <c r="H99" s="27" t="str">
         <f>Item5!K98</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I99" s="28" t="str">
         <f>Item6!K98</f>
         <v>Quantile</v>
       </c>
       <c r="J99" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="K99" s="26"/>
+        <v>129</v>
+      </c>
+      <c r="K99" s="26" t="s">
+        <v>130</v>
+      </c>
       <c r="L99" s="27">
         <v>8</v>
       </c>
@@ -5822,14 +5818,14 @@
       </c>
       <c r="H100" t="str">
         <f>Item5!K99</f>
-        <v>Log</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I100" s="4" t="str">
         <f>Item6!K99</f>
         <v>Quantile</v>
       </c>
       <c r="J100" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K100" s="8"/>
       <c r="L100">
@@ -5867,17 +5863,17 @@
       </c>
       <c r="H101" t="str">
         <f>Item5!K100</f>
-        <v>Median</v>
+        <v>CyclicLoess</v>
       </c>
       <c r="I101" s="4" t="str">
         <f>Item6!K100</f>
         <v>Quantile</v>
       </c>
       <c r="J101" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L101">
         <v>9</v>
@@ -5914,7 +5910,7 @@
       </c>
       <c r="H102" s="6" t="str">
         <f>Item5!K101</f>
-        <v>Log</v>
+        <v>Median</v>
       </c>
       <c r="I102" s="7" t="str">
         <f>Item6!K101</f>
@@ -7268,7 +7264,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="27">
         <v>4</v>
@@ -7277,7 +7273,7 @@
         <v>5</v>
       </c>
       <c r="H38" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="27">
         <v>3</v>
@@ -7286,7 +7282,7 @@
         <v>7</v>
       </c>
       <c r="K38" s="28" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -7399,7 +7395,7 @@
         <v>2</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C42" s="30">
         <v>8</v>
@@ -7924,7 +7920,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3">
         <v>6</v>
@@ -8309,7 +8305,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C68" s="3">
         <v>6</v>
@@ -9630,31 +9626,31 @@
         <v>17</v>
       </c>
       <c r="C4" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="28" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -9665,31 +9661,31 @@
         <v>95</v>
       </c>
       <c r="C5" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="28" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -10957,7 +10953,7 @@
         <v>2</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C42" s="30">
         <v>1</v>
@@ -11482,7 +11478,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3">
         <v>2</v>
@@ -11867,7 +11863,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C68" s="3">
         <v>2</v>
@@ -12325,31 +12321,31 @@
         <v>69</v>
       </c>
       <c r="C81" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G81" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J81" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81" s="28" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -14515,7 +14511,7 @@
         <v>2</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C42" s="30">
         <v>6</v>
@@ -15040,7 +15036,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3">
         <v>3</v>
@@ -15425,7 +15421,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C68" s="3">
         <v>3</v>
@@ -18074,7 +18070,7 @@
         <v>2</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C42" s="30">
         <v>4</v>
@@ -18599,7 +18595,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3">
         <v>3</v>
@@ -18984,7 +18980,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C68" s="3">
         <v>3</v>
@@ -20234,17 +20230,17 @@
       <c r="B2" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="30">
-        <v>1</v>
+      <c r="C2" s="24">
+        <v>4</v>
       </c>
       <c r="D2" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" s="27">
         <v>1</v>
@@ -20259,7 +20255,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -20270,19 +20266,19 @@
         <v>11</v>
       </c>
       <c r="C3" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3" s="27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" s="27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="27">
         <v>1</v>
@@ -20294,7 +20290,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -20305,31 +20301,31 @@
         <v>17</v>
       </c>
       <c r="C4" s="30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" s="27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" s="27">
         <v>1</v>
       </c>
       <c r="F4" s="27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4" s="27">
         <v>1</v>
       </c>
       <c r="H4" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" s="28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -20340,31 +20336,31 @@
         <v>95</v>
       </c>
       <c r="C5" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -20375,31 +20371,31 @@
         <v>70</v>
       </c>
       <c r="C6" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="27">
         <v>2</v>
       </c>
       <c r="F6" s="27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" s="27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6" s="27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -20410,16 +20406,16 @@
         <v>15</v>
       </c>
       <c r="C7" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="27">
         <v>1</v>
       </c>
       <c r="F7" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="27">
         <v>1</v>
@@ -20445,7 +20441,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -20469,7 +20465,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -20480,19 +20476,19 @@
         <v>6</v>
       </c>
       <c r="C9" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -20504,7 +20500,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -20515,31 +20511,31 @@
         <v>93</v>
       </c>
       <c r="C10" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4">
         <v>1</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -20574,7 +20570,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -20585,16 +20581,16 @@
         <v>20</v>
       </c>
       <c r="C12" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -20609,7 +20605,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -20620,16 +20616,16 @@
         <v>74</v>
       </c>
       <c r="C13" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -20644,7 +20640,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -20658,28 +20654,28 @@
         <v>3</v>
       </c>
       <c r="D14" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" s="28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -20690,19 +20686,19 @@
         <v>78</v>
       </c>
       <c r="C15" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="27">
         <v>1</v>
@@ -20714,7 +20710,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -20725,22 +20721,22 @@
         <v>83</v>
       </c>
       <c r="C16" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" s="27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="27">
         <v>3</v>
@@ -20760,31 +20756,31 @@
         <v>12</v>
       </c>
       <c r="C17" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="27">
         <v>1</v>
       </c>
       <c r="H17" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -20795,31 +20791,31 @@
         <v>16</v>
       </c>
       <c r="C18" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -20830,31 +20826,31 @@
         <v>18</v>
       </c>
       <c r="C19" s="30">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D19" s="27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E19" s="27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" s="27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G19" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="27">
         <v>1</v>
       </c>
       <c r="I19" s="27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J19" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -20865,19 +20861,19 @@
         <v>75</v>
       </c>
       <c r="C20" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -20889,7 +20885,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -20900,31 +20896,31 @@
         <v>96</v>
       </c>
       <c r="C21" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" s="4">
         <v>1</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -20934,32 +20930,32 @@
       <c r="B22" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="38">
-        <v>3</v>
-      </c>
-      <c r="D22" s="39">
-        <v>2</v>
-      </c>
-      <c r="E22" s="39">
-        <v>1</v>
-      </c>
-      <c r="F22" s="39">
-        <v>2</v>
-      </c>
-      <c r="G22" s="39">
-        <v>1</v>
-      </c>
-      <c r="H22" s="39">
-        <v>1</v>
-      </c>
-      <c r="I22" s="39">
-        <v>1</v>
-      </c>
-      <c r="J22" s="40">
-        <v>1</v>
+      <c r="C22" s="3">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" s="4">
+        <v>2</v>
       </c>
       <c r="K22" s="40" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -20970,31 +20966,31 @@
         <v>39</v>
       </c>
       <c r="C23" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J23" s="4">
         <v>1</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -21005,25 +21001,25 @@
         <v>71</v>
       </c>
       <c r="C24" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" s="4">
         <v>1</v>
@@ -21040,31 +21036,31 @@
         <v>72</v>
       </c>
       <c r="C25" s="30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" s="27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G25" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="27">
         <v>1</v>
       </c>
       <c r="I25" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -21075,31 +21071,31 @@
         <v>80</v>
       </c>
       <c r="C26" s="30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D26" s="27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" s="27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G26" s="27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H26" s="27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" s="28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K26" s="28" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -21110,16 +21106,16 @@
         <v>81</v>
       </c>
       <c r="C27" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="27">
         <v>1</v>
@@ -21134,7 +21130,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -21145,16 +21141,16 @@
         <v>82</v>
       </c>
       <c r="C28" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="27">
         <v>1</v>
       </c>
       <c r="F28" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="27">
         <v>1</v>
@@ -21169,7 +21165,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -21192,16 +21188,16 @@
         <v>5</v>
       </c>
       <c r="G29" s="27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="27">
         <v>1</v>
       </c>
       <c r="I29" s="27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J29" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" s="28" t="s">
         <v>116</v>
@@ -21250,16 +21246,16 @@
         <v>90</v>
       </c>
       <c r="C31" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -21274,7 +21270,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -21320,16 +21316,16 @@
         <v>7</v>
       </c>
       <c r="C33" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -21355,28 +21351,28 @@
         <v>13</v>
       </c>
       <c r="C34" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H34">
         <v>1</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J34" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>116</v>
@@ -21390,16 +21386,16 @@
         <v>76</v>
       </c>
       <c r="C35" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -21414,7 +21410,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -21425,16 +21421,16 @@
         <v>79</v>
       </c>
       <c r="C36" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -21460,19 +21456,19 @@
         <v>84</v>
       </c>
       <c r="C37" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" s="27">
         <v>1</v>
@@ -21484,7 +21480,7 @@
         <v>1</v>
       </c>
       <c r="K37" s="28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -21495,31 +21491,31 @@
         <v>85</v>
       </c>
       <c r="C38" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38" s="27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="27">
         <v>1</v>
       </c>
       <c r="I38" s="27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J38" s="28">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K38" s="28" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -21565,16 +21561,16 @@
         <v>91</v>
       </c>
       <c r="C40" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="27">
         <v>1</v>
       </c>
       <c r="F40" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="27">
         <v>1</v>
@@ -21600,19 +21596,19 @@
         <v>2</v>
       </c>
       <c r="C41" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D41" s="27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="27">
         <v>1</v>
@@ -21624,7 +21620,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -21632,34 +21628,34 @@
         <v>2</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C42" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D42" s="27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" s="27">
         <v>4</v>
       </c>
       <c r="G42" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42" s="27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I42" s="27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J42" s="28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K42" s="28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -21705,31 +21701,31 @@
         <v>8</v>
       </c>
       <c r="C44" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -21740,31 +21736,31 @@
         <v>89</v>
       </c>
       <c r="C45" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" s="4">
         <v>1</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -21774,32 +21770,32 @@
       <c r="B46" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C46">
-        <v>1</v>
+      <c r="C46" s="3">
+        <v>5</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46">
-        <v>1</v>
-      </c>
-      <c r="J46">
+        <v>2</v>
+      </c>
+      <c r="J46" s="4">
         <v>1</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -21810,31 +21806,31 @@
         <v>10</v>
       </c>
       <c r="C47" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J47" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -21845,31 +21841,31 @@
         <v>14</v>
       </c>
       <c r="C48" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -21915,7 +21911,7 @@
         <v>97</v>
       </c>
       <c r="C50" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" s="27">
         <v>1</v>
@@ -21939,7 +21935,7 @@
         <v>1</v>
       </c>
       <c r="K50" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -21950,31 +21946,31 @@
         <v>9</v>
       </c>
       <c r="C51" s="37">
-        <v>3</v>
-      </c>
-      <c r="D51" s="27">
-        <v>3</v>
-      </c>
-      <c r="E51" s="27">
-        <v>1</v>
-      </c>
-      <c r="F51" s="27">
-        <v>2</v>
-      </c>
-      <c r="G51" s="27">
-        <v>1</v>
-      </c>
-      <c r="H51" s="27">
+        <v>7</v>
+      </c>
+      <c r="D51" s="36">
+        <v>6</v>
+      </c>
+      <c r="E51" s="36">
+        <v>4</v>
+      </c>
+      <c r="F51" s="36">
+        <v>6</v>
+      </c>
+      <c r="G51" s="36">
+        <v>5</v>
+      </c>
+      <c r="H51" s="36">
         <v>1</v>
       </c>
       <c r="I51" s="36">
-        <v>1</v>
-      </c>
-      <c r="J51" s="28">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="J51" s="43">
+        <v>2</v>
       </c>
       <c r="K51" s="28" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -21985,31 +21981,31 @@
         <v>34</v>
       </c>
       <c r="C52" s="3">
-        <v>3</v>
-      </c>
-      <c r="D52" s="23">
-        <v>4</v>
-      </c>
-      <c r="E52" s="23">
-        <v>1</v>
-      </c>
-      <c r="F52" s="23">
-        <v>4</v>
-      </c>
-      <c r="G52" s="23">
-        <v>1</v>
-      </c>
-      <c r="H52" s="23">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>2</v>
-      </c>
-      <c r="J52" s="33">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J52" s="4">
+        <v>1</v>
       </c>
       <c r="K52" s="33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -22020,31 +22016,31 @@
         <v>30</v>
       </c>
       <c r="C53" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J53" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -22055,16 +22051,16 @@
         <v>52</v>
       </c>
       <c r="C54" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -22090,19 +22086,19 @@
         <v>27</v>
       </c>
       <c r="C55" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -22114,7 +22110,7 @@
         <v>1</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -22125,19 +22121,19 @@
         <v>25</v>
       </c>
       <c r="C56" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -22149,7 +22145,7 @@
         <v>1</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -22157,19 +22153,19 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -22184,7 +22180,7 @@
         <v>1</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -22194,32 +22190,32 @@
       <c r="B58" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="30">
-        <v>2</v>
-      </c>
-      <c r="D58" s="27">
-        <v>2</v>
-      </c>
-      <c r="E58" s="27">
-        <v>1</v>
-      </c>
-      <c r="F58" s="27">
-        <v>2</v>
-      </c>
-      <c r="G58" s="27">
-        <v>1</v>
-      </c>
-      <c r="H58" s="27">
-        <v>1</v>
-      </c>
-      <c r="I58" s="27">
-        <v>1</v>
-      </c>
-      <c r="J58" s="28">
-        <v>1</v>
-      </c>
-      <c r="K58" s="28" t="s">
-        <v>113</v>
+      <c r="C58" s="3">
+        <v>3</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="F58">
+        <v>4</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58" s="4">
+        <v>1</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -22230,16 +22226,16 @@
         <v>51</v>
       </c>
       <c r="C59" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="27">
         <v>1</v>
       </c>
       <c r="F59" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" s="27">
         <v>1</v>
@@ -22254,7 +22250,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -22265,31 +22261,31 @@
         <v>56</v>
       </c>
       <c r="C60" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" s="27">
         <v>1</v>
       </c>
       <c r="H60" s="27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I60" s="27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J60" s="28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K60" s="28" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -22303,13 +22299,13 @@
         <v>1</v>
       </c>
       <c r="D61" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="27">
         <v>1</v>
       </c>
       <c r="F61" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" s="27">
         <v>1</v>
@@ -22335,16 +22331,16 @@
         <v>61</v>
       </c>
       <c r="C62" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" s="27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G62" s="27">
         <v>1</v>
@@ -22359,7 +22355,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="28" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -22405,16 +22401,16 @@
         <v>31</v>
       </c>
       <c r="C64" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -22429,7 +22425,7 @@
         <v>1</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -22440,16 +22436,16 @@
         <v>35</v>
       </c>
       <c r="C65" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -22464,7 +22460,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -22475,19 +22471,19 @@
         <v>57</v>
       </c>
       <c r="C66" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -22499,7 +22495,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -22510,19 +22506,19 @@
         <v>22</v>
       </c>
       <c r="C67" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -22534,7 +22530,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -22542,19 +22538,19 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C68" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -22569,7 +22565,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -22580,31 +22576,31 @@
         <v>54</v>
       </c>
       <c r="C69" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="4">
         <v>2</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -22615,19 +22611,19 @@
         <v>53</v>
       </c>
       <c r="C70" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D70" s="27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E70" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F70" s="27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G70" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" s="27">
         <v>1</v>
@@ -22639,7 +22635,7 @@
         <v>1</v>
       </c>
       <c r="K70" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -22650,16 +22646,16 @@
         <v>55</v>
       </c>
       <c r="C71" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" s="27">
         <v>1</v>
       </c>
       <c r="F71" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" s="27">
         <v>1</v>
@@ -22674,7 +22670,7 @@
         <v>1</v>
       </c>
       <c r="K71" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -22685,31 +22681,31 @@
         <v>58</v>
       </c>
       <c r="C72" s="30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D72" s="27">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E72" s="27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F72" s="27">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G72" s="27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H72" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J72" s="28">
         <v>2</v>
       </c>
       <c r="K72" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -22723,28 +22719,28 @@
         <v>6</v>
       </c>
       <c r="D73" s="27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E73" s="27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F73" s="27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G73" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H73" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73" s="27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J73" s="28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K73" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -22755,16 +22751,16 @@
         <v>62</v>
       </c>
       <c r="C74" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" s="27">
         <v>1</v>
       </c>
       <c r="F74" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="27">
         <v>1</v>
@@ -22779,7 +22775,7 @@
         <v>1</v>
       </c>
       <c r="K74" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -22790,19 +22786,19 @@
         <v>63</v>
       </c>
       <c r="C75" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -22814,7 +22810,7 @@
         <v>1</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -22825,19 +22821,19 @@
         <v>41</v>
       </c>
       <c r="C76" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -22846,10 +22842,10 @@
         <v>1</v>
       </c>
       <c r="J76" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -22860,31 +22856,31 @@
         <v>42</v>
       </c>
       <c r="C77" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77" s="4">
         <v>1</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -22895,31 +22891,31 @@
         <v>44</v>
       </c>
       <c r="C78" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D78">
         <v>5</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F78">
         <v>5</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J78" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -22933,13 +22929,13 @@
         <v>2</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -22968,13 +22964,13 @@
         <v>2</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -23000,31 +22996,31 @@
         <v>69</v>
       </c>
       <c r="C81" s="30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D81" s="27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81" s="27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F81" s="27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G81" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81" s="27">
         <v>1</v>
       </c>
       <c r="I81" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J81" s="28">
         <v>1</v>
       </c>
       <c r="K81" s="28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -23035,16 +23031,16 @@
         <v>45</v>
       </c>
       <c r="C82" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D82" s="27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G82" s="27">
         <v>1</v>
@@ -23059,7 +23055,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="28" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -23070,16 +23066,16 @@
         <v>32</v>
       </c>
       <c r="C83" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D83" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -23094,7 +23090,7 @@
         <v>1</v>
       </c>
       <c r="K83" s="28" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -23105,31 +23101,31 @@
         <v>40</v>
       </c>
       <c r="C84" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D84" s="27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E84" s="27">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F84" s="27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G84" s="27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H84" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J84" s="28">
         <v>1</v>
       </c>
       <c r="K84" s="28" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -23140,19 +23136,19 @@
         <v>50</v>
       </c>
       <c r="C85" s="30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D85" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E85" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F85" s="27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H85" s="27">
         <v>1</v>
@@ -23164,7 +23160,7 @@
         <v>1</v>
       </c>
       <c r="K85" s="28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -23175,16 +23171,16 @@
         <v>67</v>
       </c>
       <c r="C86" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" s="27">
         <v>1</v>
       </c>
       <c r="F86" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G86" s="27">
         <v>1</v>
@@ -23199,7 +23195,7 @@
         <v>1</v>
       </c>
       <c r="K86" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -23210,16 +23206,16 @@
         <v>21</v>
       </c>
       <c r="C87" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87">
         <v>2</v>
       </c>
       <c r="E87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -23234,7 +23230,7 @@
         <v>1</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -23248,13 +23244,13 @@
         <v>1</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88">
         <v>1</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -23280,7 +23276,7 @@
         <v>48</v>
       </c>
       <c r="C89" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -23304,7 +23300,7 @@
         <v>1</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -23315,31 +23311,31 @@
         <v>28</v>
       </c>
       <c r="C90" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E90">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" s="4">
         <v>1</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -23350,16 +23346,16 @@
         <v>68</v>
       </c>
       <c r="C91" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91">
         <v>2</v>
       </c>
       <c r="E91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -23385,7 +23381,7 @@
         <v>33</v>
       </c>
       <c r="C92" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -23409,7 +23405,7 @@
         <v>1</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -23423,13 +23419,13 @@
         <v>1</v>
       </c>
       <c r="D93" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" s="27">
         <v>1</v>
       </c>
       <c r="F93" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" s="27">
         <v>1</v>
@@ -23455,16 +23451,16 @@
         <v>29</v>
       </c>
       <c r="C94" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D94" s="27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E94" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G94" s="27">
         <v>1</v>
@@ -23479,7 +23475,7 @@
         <v>1</v>
       </c>
       <c r="K94" s="28" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -23490,31 +23486,31 @@
         <v>38</v>
       </c>
       <c r="C95" s="30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D95" s="27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E95" s="27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F95" s="27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G95" s="27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H95" s="27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I95" s="27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J95" s="28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K95" s="28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -23560,28 +23556,28 @@
         <v>65</v>
       </c>
       <c r="C97" s="30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D97" s="27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E97" s="27">
         <v>1</v>
       </c>
       <c r="F97" s="27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G97" s="27">
         <v>1</v>
       </c>
       <c r="H97" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I97" s="27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J97" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K97" s="28" t="s">
         <v>113</v>
@@ -23595,31 +23591,31 @@
         <v>23</v>
       </c>
       <c r="C98" s="30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D98" s="27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E98" s="27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F98" s="27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G98" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H98" s="27">
         <v>1</v>
       </c>
       <c r="I98" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J98" s="28">
         <v>1</v>
       </c>
       <c r="K98" s="28" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -23630,19 +23626,19 @@
         <v>24</v>
       </c>
       <c r="C99" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -23654,7 +23650,7 @@
         <v>1</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -23665,31 +23661,31 @@
         <v>37</v>
       </c>
       <c r="C100" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E100">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F100">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H100">
         <v>1</v>
       </c>
       <c r="I100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J100" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -23700,16 +23696,16 @@
         <v>36</v>
       </c>
       <c r="C101" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E101" s="6">
         <v>1</v>
       </c>
       <c r="F101" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G101" s="6">
         <v>1</v>
@@ -23724,7 +23720,7 @@
         <v>1</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -25190,7 +25186,7 @@
         <v>2</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C42" s="30">
         <v>5</v>
@@ -25715,7 +25711,7 @@
         <v>27</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3">
         <v>3</v>
@@ -26100,7 +26096,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C68" s="3">
         <v>3</v>
@@ -27283,6 +27279,3564 @@
       </c>
       <c r="K101" s="7" t="s">
         <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE129214-63C4-4DEE-930E-ED99E3F4A977}">
+  <dimension ref="A1:K101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="H1" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="35" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="30">
+        <v>75</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="30">
+        <v>1</v>
+      </c>
+      <c r="D2" s="27">
+        <v>1</v>
+      </c>
+      <c r="E2" s="27">
+        <v>1</v>
+      </c>
+      <c r="F2" s="27">
+        <v>1</v>
+      </c>
+      <c r="G2" s="27">
+        <v>1</v>
+      </c>
+      <c r="H2" s="27">
+        <v>1</v>
+      </c>
+      <c r="I2" s="27">
+        <v>1</v>
+      </c>
+      <c r="J2" s="28">
+        <v>1</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="30">
+        <v>11</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="30">
+        <v>1</v>
+      </c>
+      <c r="D3" s="27">
+        <v>1</v>
+      </c>
+      <c r="E3" s="27">
+        <v>1</v>
+      </c>
+      <c r="F3" s="27">
+        <v>1</v>
+      </c>
+      <c r="G3" s="27">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27">
+        <v>1</v>
+      </c>
+      <c r="I3" s="27">
+        <v>1</v>
+      </c>
+      <c r="J3" s="28">
+        <v>1</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="30">
+        <v>17</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="30">
+        <v>5</v>
+      </c>
+      <c r="D4" s="27">
+        <v>4</v>
+      </c>
+      <c r="E4" s="27">
+        <v>1</v>
+      </c>
+      <c r="F4" s="27">
+        <v>4</v>
+      </c>
+      <c r="G4" s="27">
+        <v>1</v>
+      </c>
+      <c r="H4" s="27">
+        <v>2</v>
+      </c>
+      <c r="I4" s="27">
+        <v>2</v>
+      </c>
+      <c r="J4" s="28">
+        <v>3</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="30">
+        <v>98</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="30">
+        <v>5</v>
+      </c>
+      <c r="D5" s="27">
+        <v>4</v>
+      </c>
+      <c r="E5" s="27">
+        <v>3</v>
+      </c>
+      <c r="F5" s="27">
+        <v>4</v>
+      </c>
+      <c r="G5" s="27">
+        <v>1</v>
+      </c>
+      <c r="H5" s="27">
+        <v>2</v>
+      </c>
+      <c r="I5" s="27">
+        <v>3</v>
+      </c>
+      <c r="J5" s="28">
+        <v>3</v>
+      </c>
+      <c r="K5" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="30">
+        <v>72</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="30">
+        <v>6</v>
+      </c>
+      <c r="D6" s="27">
+        <v>5</v>
+      </c>
+      <c r="E6" s="27">
+        <v>2</v>
+      </c>
+      <c r="F6" s="27">
+        <v>5</v>
+      </c>
+      <c r="G6" s="27">
+        <v>1</v>
+      </c>
+      <c r="H6" s="27">
+        <v>4</v>
+      </c>
+      <c r="I6" s="27">
+        <v>4</v>
+      </c>
+      <c r="J6" s="28">
+        <v>3</v>
+      </c>
+      <c r="K6" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="30">
+        <v>15</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="30">
+        <v>2</v>
+      </c>
+      <c r="D7" s="27">
+        <v>1</v>
+      </c>
+      <c r="E7" s="27">
+        <v>1</v>
+      </c>
+      <c r="F7" s="27">
+        <v>1</v>
+      </c>
+      <c r="G7" s="27">
+        <v>1</v>
+      </c>
+      <c r="H7" s="27">
+        <v>1</v>
+      </c>
+      <c r="I7" s="27">
+        <v>1</v>
+      </c>
+      <c r="J7" s="28">
+        <v>1</v>
+      </c>
+      <c r="K7" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>96</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>20</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>76</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="30">
+        <v>79</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="30">
+        <v>3</v>
+      </c>
+      <c r="D14" s="27">
+        <v>1</v>
+      </c>
+      <c r="E14" s="27">
+        <v>2</v>
+      </c>
+      <c r="F14" s="27">
+        <v>1</v>
+      </c>
+      <c r="G14" s="27">
+        <v>2</v>
+      </c>
+      <c r="H14" s="27">
+        <v>2</v>
+      </c>
+      <c r="I14" s="27">
+        <v>2</v>
+      </c>
+      <c r="J14" s="28">
+        <v>2</v>
+      </c>
+      <c r="K14" s="28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="30">
+        <v>80</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="30">
+        <v>3</v>
+      </c>
+      <c r="D15" s="27">
+        <v>2</v>
+      </c>
+      <c r="E15" s="27">
+        <v>1</v>
+      </c>
+      <c r="F15" s="27">
+        <v>2</v>
+      </c>
+      <c r="G15" s="27">
+        <v>1</v>
+      </c>
+      <c r="H15" s="27">
+        <v>1</v>
+      </c>
+      <c r="I15" s="27">
+        <v>1</v>
+      </c>
+      <c r="J15" s="28">
+        <v>1</v>
+      </c>
+      <c r="K15" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="30">
+        <v>85</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="30">
+        <v>5</v>
+      </c>
+      <c r="D16" s="27">
+        <v>4</v>
+      </c>
+      <c r="E16" s="27">
+        <v>2</v>
+      </c>
+      <c r="F16" s="27">
+        <v>4</v>
+      </c>
+      <c r="G16" s="27">
+        <v>1</v>
+      </c>
+      <c r="H16" s="27">
+        <v>2</v>
+      </c>
+      <c r="I16" s="27">
+        <v>3</v>
+      </c>
+      <c r="J16" s="28">
+        <v>2</v>
+      </c>
+      <c r="K16" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="30">
+        <v>12</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="30">
+        <v>2</v>
+      </c>
+      <c r="D17" s="27">
+        <v>3</v>
+      </c>
+      <c r="E17" s="27">
+        <v>1</v>
+      </c>
+      <c r="F17" s="27">
+        <v>3</v>
+      </c>
+      <c r="G17" s="27">
+        <v>1</v>
+      </c>
+      <c r="H17" s="27">
+        <v>1</v>
+      </c>
+      <c r="I17" s="27">
+        <v>1</v>
+      </c>
+      <c r="J17" s="28">
+        <v>1</v>
+      </c>
+      <c r="K17" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="30">
+        <v>16</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="30">
+        <v>4</v>
+      </c>
+      <c r="D18" s="27">
+        <v>3</v>
+      </c>
+      <c r="E18" s="27">
+        <v>1</v>
+      </c>
+      <c r="F18" s="27">
+        <v>3</v>
+      </c>
+      <c r="G18" s="27">
+        <v>1</v>
+      </c>
+      <c r="H18" s="27">
+        <v>2</v>
+      </c>
+      <c r="I18" s="27">
+        <v>2</v>
+      </c>
+      <c r="J18" s="28">
+        <v>2</v>
+      </c>
+      <c r="K18" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="30">
+        <v>18</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="30">
+        <v>2</v>
+      </c>
+      <c r="D19" s="27">
+        <v>1</v>
+      </c>
+      <c r="E19" s="27">
+        <v>1</v>
+      </c>
+      <c r="F19" s="27">
+        <v>1</v>
+      </c>
+      <c r="G19" s="27">
+        <v>1</v>
+      </c>
+      <c r="H19" s="27">
+        <v>1</v>
+      </c>
+      <c r="I19" s="27">
+        <v>1</v>
+      </c>
+      <c r="J19" s="28">
+        <v>1</v>
+      </c>
+      <c r="K19" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>77</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4">
+        <v>1</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>99</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21" s="4">
+        <v>1</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="38">
+        <v>19</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="38">
+        <v>3</v>
+      </c>
+      <c r="D22" s="39">
+        <v>2</v>
+      </c>
+      <c r="E22" s="39">
+        <v>1</v>
+      </c>
+      <c r="F22" s="39">
+        <v>2</v>
+      </c>
+      <c r="G22" s="39">
+        <v>1</v>
+      </c>
+      <c r="H22" s="39">
+        <v>1</v>
+      </c>
+      <c r="I22" s="39">
+        <v>1</v>
+      </c>
+      <c r="J22" s="40">
+        <v>1</v>
+      </c>
+      <c r="K22" s="40" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="3">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23" s="4">
+        <v>1</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>73</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="3">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4">
+        <v>1</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="30">
+        <v>74</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="30">
+        <v>2</v>
+      </c>
+      <c r="D25" s="27">
+        <v>2</v>
+      </c>
+      <c r="E25" s="27">
+        <v>1</v>
+      </c>
+      <c r="F25" s="27">
+        <v>2</v>
+      </c>
+      <c r="G25" s="27">
+        <v>1</v>
+      </c>
+      <c r="H25" s="27">
+        <v>1</v>
+      </c>
+      <c r="I25" s="27">
+        <v>1</v>
+      </c>
+      <c r="J25" s="28">
+        <v>1</v>
+      </c>
+      <c r="K25" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="30">
+        <v>82</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="30">
+        <v>8</v>
+      </c>
+      <c r="D26" s="27">
+        <v>7</v>
+      </c>
+      <c r="E26" s="27">
+        <v>5</v>
+      </c>
+      <c r="F26" s="27">
+        <v>1</v>
+      </c>
+      <c r="G26" s="27">
+        <v>6</v>
+      </c>
+      <c r="H26" s="27">
+        <v>3</v>
+      </c>
+      <c r="I26" s="27">
+        <v>2</v>
+      </c>
+      <c r="J26" s="28">
+        <v>4</v>
+      </c>
+      <c r="K26" s="28" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="30">
+        <v>83</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="30">
+        <v>2</v>
+      </c>
+      <c r="D27" s="27">
+        <v>1</v>
+      </c>
+      <c r="E27" s="27">
+        <v>1</v>
+      </c>
+      <c r="F27" s="27">
+        <v>1</v>
+      </c>
+      <c r="G27" s="27">
+        <v>1</v>
+      </c>
+      <c r="H27" s="27">
+        <v>1</v>
+      </c>
+      <c r="I27" s="27">
+        <v>1</v>
+      </c>
+      <c r="J27" s="28">
+        <v>1</v>
+      </c>
+      <c r="K27" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="30">
+        <v>84</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="30">
+        <v>1</v>
+      </c>
+      <c r="D28" s="27">
+        <v>1</v>
+      </c>
+      <c r="E28" s="27">
+        <v>1</v>
+      </c>
+      <c r="F28" s="27">
+        <v>1</v>
+      </c>
+      <c r="G28" s="27">
+        <v>1</v>
+      </c>
+      <c r="H28" s="27">
+        <v>1</v>
+      </c>
+      <c r="I28" s="27">
+        <v>1</v>
+      </c>
+      <c r="J28" s="28">
+        <v>1</v>
+      </c>
+      <c r="K28" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="30">
+        <v>88</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="30">
+        <v>6</v>
+      </c>
+      <c r="D29" s="27">
+        <v>5</v>
+      </c>
+      <c r="E29" s="27">
+        <v>4</v>
+      </c>
+      <c r="F29" s="27">
+        <v>5</v>
+      </c>
+      <c r="G29" s="27">
+        <v>4</v>
+      </c>
+      <c r="H29" s="27">
+        <v>1</v>
+      </c>
+      <c r="I29" s="27">
+        <v>3</v>
+      </c>
+      <c r="J29" s="28">
+        <v>2</v>
+      </c>
+      <c r="K29" s="28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="30">
+        <v>90</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="30">
+        <v>3</v>
+      </c>
+      <c r="D30" s="27">
+        <v>2</v>
+      </c>
+      <c r="E30" s="27">
+        <v>1</v>
+      </c>
+      <c r="F30" s="27">
+        <v>2</v>
+      </c>
+      <c r="G30" s="27">
+        <v>1</v>
+      </c>
+      <c r="H30" s="27">
+        <v>1</v>
+      </c>
+      <c r="I30" s="27">
+        <v>1</v>
+      </c>
+      <c r="J30" s="28">
+        <v>1</v>
+      </c>
+      <c r="K30" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>93</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="3">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" s="4">
+        <v>1</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>95</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="3">
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" s="4">
+        <v>1</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>7</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" s="4">
+        <v>1</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>13</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="3">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4">
+        <v>1</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>78</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="3">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35" s="4">
+        <v>1</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>81</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="3">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36" s="4">
+        <v>1</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="34">
+        <v>86</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="30">
+        <v>4</v>
+      </c>
+      <c r="D37" s="27">
+        <v>3</v>
+      </c>
+      <c r="E37" s="27">
+        <v>2</v>
+      </c>
+      <c r="F37" s="27">
+        <v>3</v>
+      </c>
+      <c r="G37" s="27">
+        <v>1</v>
+      </c>
+      <c r="H37" s="27">
+        <v>1</v>
+      </c>
+      <c r="I37" s="27">
+        <v>1</v>
+      </c>
+      <c r="J37" s="28">
+        <v>1</v>
+      </c>
+      <c r="K37" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="30">
+        <v>87</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="30">
+        <v>6</v>
+      </c>
+      <c r="D38" s="27">
+        <v>5</v>
+      </c>
+      <c r="E38" s="27">
+        <v>3</v>
+      </c>
+      <c r="F38" s="27">
+        <v>5</v>
+      </c>
+      <c r="G38" s="27">
+        <v>2</v>
+      </c>
+      <c r="H38" s="27">
+        <v>1</v>
+      </c>
+      <c r="I38" s="27">
+        <v>4</v>
+      </c>
+      <c r="J38" s="28">
+        <v>7</v>
+      </c>
+      <c r="K38" s="28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="30">
+        <v>89</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="30">
+        <v>3</v>
+      </c>
+      <c r="D39" s="27">
+        <v>2</v>
+      </c>
+      <c r="E39" s="27">
+        <v>1</v>
+      </c>
+      <c r="F39" s="27">
+        <v>2</v>
+      </c>
+      <c r="G39" s="27">
+        <v>1</v>
+      </c>
+      <c r="H39" s="27">
+        <v>1</v>
+      </c>
+      <c r="I39" s="27">
+        <v>1</v>
+      </c>
+      <c r="J39" s="28">
+        <v>1</v>
+      </c>
+      <c r="K39" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="30">
+        <v>94</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="30">
+        <v>2</v>
+      </c>
+      <c r="D40" s="27">
+        <v>1</v>
+      </c>
+      <c r="E40" s="27">
+        <v>1</v>
+      </c>
+      <c r="F40" s="27">
+        <v>1</v>
+      </c>
+      <c r="G40" s="27">
+        <v>1</v>
+      </c>
+      <c r="H40" s="27">
+        <v>1</v>
+      </c>
+      <c r="I40" s="27">
+        <v>1</v>
+      </c>
+      <c r="J40" s="28">
+        <v>1</v>
+      </c>
+      <c r="K40" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="30">
+        <v>1</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="30">
+        <v>3</v>
+      </c>
+      <c r="D41" s="27">
+        <v>2</v>
+      </c>
+      <c r="E41" s="27">
+        <v>1</v>
+      </c>
+      <c r="F41" s="27">
+        <v>2</v>
+      </c>
+      <c r="G41" s="27">
+        <v>1</v>
+      </c>
+      <c r="H41" s="27">
+        <v>1</v>
+      </c>
+      <c r="I41" s="27">
+        <v>1</v>
+      </c>
+      <c r="J41" s="28">
+        <v>1</v>
+      </c>
+      <c r="K41" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="30">
+        <v>2</v>
+      </c>
+      <c r="B42" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" s="30">
+        <v>6</v>
+      </c>
+      <c r="D42" s="27">
+        <v>5</v>
+      </c>
+      <c r="E42" s="27">
+        <v>2</v>
+      </c>
+      <c r="F42" s="27">
+        <v>4</v>
+      </c>
+      <c r="G42" s="27">
+        <v>1</v>
+      </c>
+      <c r="H42" s="27">
+        <v>3</v>
+      </c>
+      <c r="I42" s="27">
+        <v>3</v>
+      </c>
+      <c r="J42" s="28">
+        <v>3</v>
+      </c>
+      <c r="K42" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>3</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="3">
+        <v>3</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43" s="4">
+        <v>1</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>8</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="3">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44" s="4">
+        <v>1</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>92</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="3">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45" s="4">
+        <v>1</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>97</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>10</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="3">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47" s="4">
+        <v>1</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>14</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="3">
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48" s="4">
+        <v>2</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="30">
+        <v>91</v>
+      </c>
+      <c r="B49" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="C49" s="30">
+        <v>3</v>
+      </c>
+      <c r="D49" s="27">
+        <v>2</v>
+      </c>
+      <c r="E49" s="27">
+        <v>1</v>
+      </c>
+      <c r="F49" s="27">
+        <v>2</v>
+      </c>
+      <c r="G49" s="27">
+        <v>1</v>
+      </c>
+      <c r="H49" s="27">
+        <v>1</v>
+      </c>
+      <c r="I49" s="27">
+        <v>1</v>
+      </c>
+      <c r="J49" s="28">
+        <v>1</v>
+      </c>
+      <c r="K49" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="30">
+        <v>100</v>
+      </c>
+      <c r="B50" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="30">
+        <v>1</v>
+      </c>
+      <c r="D50" s="27">
+        <v>1</v>
+      </c>
+      <c r="E50" s="27">
+        <v>1</v>
+      </c>
+      <c r="F50" s="27">
+        <v>1</v>
+      </c>
+      <c r="G50" s="27">
+        <v>1</v>
+      </c>
+      <c r="H50" s="27">
+        <v>1</v>
+      </c>
+      <c r="I50" s="27">
+        <v>1</v>
+      </c>
+      <c r="J50" s="28">
+        <v>1</v>
+      </c>
+      <c r="K50" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="30">
+        <v>9</v>
+      </c>
+      <c r="B51" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="37">
+        <v>3</v>
+      </c>
+      <c r="D51" s="27">
+        <v>3</v>
+      </c>
+      <c r="E51" s="27">
+        <v>1</v>
+      </c>
+      <c r="F51" s="27">
+        <v>2</v>
+      </c>
+      <c r="G51" s="27">
+        <v>1</v>
+      </c>
+      <c r="H51" s="27">
+        <v>1</v>
+      </c>
+      <c r="I51" s="36">
+        <v>1</v>
+      </c>
+      <c r="J51" s="28">
+        <v>1</v>
+      </c>
+      <c r="K51" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="20">
+        <v>36</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="3">
+        <v>3</v>
+      </c>
+      <c r="D52" s="23">
+        <v>4</v>
+      </c>
+      <c r="E52" s="23">
+        <v>1</v>
+      </c>
+      <c r="F52" s="23">
+        <v>4</v>
+      </c>
+      <c r="G52" s="23">
+        <v>1</v>
+      </c>
+      <c r="H52" s="23">
+        <v>2</v>
+      </c>
+      <c r="I52">
+        <v>2</v>
+      </c>
+      <c r="J52" s="33">
+        <v>2</v>
+      </c>
+      <c r="K52" s="33" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>32</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="3">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>4</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>3</v>
+      </c>
+      <c r="I53">
+        <v>3</v>
+      </c>
+      <c r="J53" s="4">
+        <v>3</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>54</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C54" s="3">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54" s="4">
+        <v>1</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>29</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" s="3">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55" s="4">
+        <v>1</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>26</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56" s="4">
+        <v>1</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>27</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57" s="4">
+        <v>1</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="30">
+        <v>48</v>
+      </c>
+      <c r="B58" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="30">
+        <v>2</v>
+      </c>
+      <c r="D58" s="27">
+        <v>2</v>
+      </c>
+      <c r="E58" s="27">
+        <v>1</v>
+      </c>
+      <c r="F58" s="27">
+        <v>2</v>
+      </c>
+      <c r="G58" s="27">
+        <v>1</v>
+      </c>
+      <c r="H58" s="27">
+        <v>1</v>
+      </c>
+      <c r="I58" s="27">
+        <v>1</v>
+      </c>
+      <c r="J58" s="28">
+        <v>1</v>
+      </c>
+      <c r="K58" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="30">
+        <v>53</v>
+      </c>
+      <c r="B59" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" s="30">
+        <v>1</v>
+      </c>
+      <c r="D59" s="27">
+        <v>1</v>
+      </c>
+      <c r="E59" s="27">
+        <v>1</v>
+      </c>
+      <c r="F59" s="27">
+        <v>1</v>
+      </c>
+      <c r="G59" s="27">
+        <v>1</v>
+      </c>
+      <c r="H59" s="27">
+        <v>1</v>
+      </c>
+      <c r="I59" s="27">
+        <v>1</v>
+      </c>
+      <c r="J59" s="28">
+        <v>1</v>
+      </c>
+      <c r="K59" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="30">
+        <v>58</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C60" s="30">
+        <v>2</v>
+      </c>
+      <c r="D60" s="27">
+        <v>2</v>
+      </c>
+      <c r="E60" s="27">
+        <v>2</v>
+      </c>
+      <c r="F60" s="27">
+        <v>2</v>
+      </c>
+      <c r="G60" s="27">
+        <v>1</v>
+      </c>
+      <c r="H60" s="27">
+        <v>5</v>
+      </c>
+      <c r="I60" s="27">
+        <v>3</v>
+      </c>
+      <c r="J60" s="28">
+        <v>4</v>
+      </c>
+      <c r="K60" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="30">
+        <v>62</v>
+      </c>
+      <c r="B61" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C61" s="30">
+        <v>1</v>
+      </c>
+      <c r="D61" s="27">
+        <v>1</v>
+      </c>
+      <c r="E61" s="27">
+        <v>1</v>
+      </c>
+      <c r="F61" s="27">
+        <v>1</v>
+      </c>
+      <c r="G61" s="27">
+        <v>1</v>
+      </c>
+      <c r="H61" s="27">
+        <v>1</v>
+      </c>
+      <c r="I61" s="27">
+        <v>1</v>
+      </c>
+      <c r="J61" s="28">
+        <v>1</v>
+      </c>
+      <c r="K61" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="30">
+        <v>63</v>
+      </c>
+      <c r="B62" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" s="30">
+        <v>1</v>
+      </c>
+      <c r="D62" s="27">
+        <v>2</v>
+      </c>
+      <c r="E62" s="27">
+        <v>1</v>
+      </c>
+      <c r="F62" s="27">
+        <v>2</v>
+      </c>
+      <c r="G62" s="27">
+        <v>1</v>
+      </c>
+      <c r="H62" s="27">
+        <v>1</v>
+      </c>
+      <c r="I62" s="27">
+        <v>1</v>
+      </c>
+      <c r="J62" s="28">
+        <v>1</v>
+      </c>
+      <c r="K62" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="30">
+        <v>68</v>
+      </c>
+      <c r="B63" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C63" s="30">
+        <v>3</v>
+      </c>
+      <c r="D63" s="27">
+        <v>2</v>
+      </c>
+      <c r="E63" s="27">
+        <v>1</v>
+      </c>
+      <c r="F63" s="27">
+        <v>2</v>
+      </c>
+      <c r="G63" s="27">
+        <v>1</v>
+      </c>
+      <c r="H63" s="27">
+        <v>1</v>
+      </c>
+      <c r="I63" s="27">
+        <v>1</v>
+      </c>
+      <c r="J63" s="28">
+        <v>1</v>
+      </c>
+      <c r="K63" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>33</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1</v>
+      </c>
+      <c r="D64">
+        <v>2</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>2</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64" s="4">
+        <v>1</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>37</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C65" s="3">
+        <v>2</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65" s="4">
+        <v>1</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>59</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66" s="4">
+        <v>1</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>22</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" s="3">
+        <v>2</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67" s="4">
+        <v>1</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <v>23</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68" s="4">
+        <v>1</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <v>56</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C69" s="3">
+        <v>3</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69">
+        <v>4</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>2</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69" s="4">
+        <v>2</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="30">
+        <v>55</v>
+      </c>
+      <c r="B70" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C70" s="30">
+        <v>3</v>
+      </c>
+      <c r="D70" s="27">
+        <v>2</v>
+      </c>
+      <c r="E70" s="27">
+        <v>1</v>
+      </c>
+      <c r="F70" s="27">
+        <v>2</v>
+      </c>
+      <c r="G70" s="27">
+        <v>1</v>
+      </c>
+      <c r="H70" s="27">
+        <v>1</v>
+      </c>
+      <c r="I70" s="27">
+        <v>1</v>
+      </c>
+      <c r="J70" s="28">
+        <v>1</v>
+      </c>
+      <c r="K70" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="30">
+        <v>57</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C71" s="30">
+        <v>1</v>
+      </c>
+      <c r="D71" s="27">
+        <v>2</v>
+      </c>
+      <c r="E71" s="27">
+        <v>1</v>
+      </c>
+      <c r="F71" s="27">
+        <v>2</v>
+      </c>
+      <c r="G71" s="27">
+        <v>1</v>
+      </c>
+      <c r="H71" s="27">
+        <v>1</v>
+      </c>
+      <c r="I71" s="27">
+        <v>1</v>
+      </c>
+      <c r="J71" s="28">
+        <v>1</v>
+      </c>
+      <c r="K71" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="30">
+        <v>60</v>
+      </c>
+      <c r="B72" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="30">
+        <v>4</v>
+      </c>
+      <c r="D72" s="27">
+        <v>3</v>
+      </c>
+      <c r="E72" s="27">
+        <v>1</v>
+      </c>
+      <c r="F72" s="27">
+        <v>3</v>
+      </c>
+      <c r="G72" s="27">
+        <v>1</v>
+      </c>
+      <c r="H72" s="27">
+        <v>2</v>
+      </c>
+      <c r="I72" s="27">
+        <v>2</v>
+      </c>
+      <c r="J72" s="28">
+        <v>2</v>
+      </c>
+      <c r="K72" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="30">
+        <v>61</v>
+      </c>
+      <c r="B73" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C73" s="30">
+        <v>6</v>
+      </c>
+      <c r="D73" s="27">
+        <v>5</v>
+      </c>
+      <c r="E73" s="27">
+        <v>1</v>
+      </c>
+      <c r="F73" s="27">
+        <v>5</v>
+      </c>
+      <c r="G73" s="27">
+        <v>1</v>
+      </c>
+      <c r="H73" s="27">
+        <v>2</v>
+      </c>
+      <c r="I73" s="27">
+        <v>3</v>
+      </c>
+      <c r="J73" s="28">
+        <v>4</v>
+      </c>
+      <c r="K73" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="30">
+        <v>64</v>
+      </c>
+      <c r="B74" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C74" s="30">
+        <v>1</v>
+      </c>
+      <c r="D74" s="27">
+        <v>1</v>
+      </c>
+      <c r="E74" s="27">
+        <v>1</v>
+      </c>
+      <c r="F74" s="27">
+        <v>1</v>
+      </c>
+      <c r="G74" s="27">
+        <v>1</v>
+      </c>
+      <c r="H74" s="27">
+        <v>1</v>
+      </c>
+      <c r="I74" s="27">
+        <v>1</v>
+      </c>
+      <c r="J74" s="28">
+        <v>1</v>
+      </c>
+      <c r="K74" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <v>65</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C75" s="3">
+        <v>2</v>
+      </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75" s="4">
+        <v>1</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <v>43</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" s="3">
+        <v>2</v>
+      </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76" s="4">
+        <v>4</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>44</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C77" s="3">
+        <v>2</v>
+      </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77" s="4">
+        <v>1</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>46</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C78" s="3">
+        <v>4</v>
+      </c>
+      <c r="D78">
+        <v>5</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="F78">
+        <v>5</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>3</v>
+      </c>
+      <c r="I78">
+        <v>3</v>
+      </c>
+      <c r="J78" s="4">
+        <v>3</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>49</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C79" s="3">
+        <v>2</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79" s="4">
+        <v>1</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>51</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C80" s="3">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80">
+        <v>2</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80" s="4">
+        <v>1</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="30">
+        <v>71</v>
+      </c>
+      <c r="B81" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C81" s="30">
+        <v>5</v>
+      </c>
+      <c r="D81" s="27">
+        <v>4</v>
+      </c>
+      <c r="E81" s="27">
+        <v>3</v>
+      </c>
+      <c r="F81" s="27">
+        <v>4</v>
+      </c>
+      <c r="G81" s="27">
+        <v>1</v>
+      </c>
+      <c r="H81" s="27">
+        <v>1</v>
+      </c>
+      <c r="I81" s="27">
+        <v>2</v>
+      </c>
+      <c r="J81" s="28">
+        <v>1</v>
+      </c>
+      <c r="K81" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="30">
+        <v>47</v>
+      </c>
+      <c r="B82" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C82" s="30">
+        <v>1</v>
+      </c>
+      <c r="D82" s="27">
+        <v>1</v>
+      </c>
+      <c r="E82" s="27">
+        <v>1</v>
+      </c>
+      <c r="F82" s="27">
+        <v>1</v>
+      </c>
+      <c r="G82" s="27">
+        <v>1</v>
+      </c>
+      <c r="H82" s="27">
+        <v>1</v>
+      </c>
+      <c r="I82" s="27">
+        <v>1</v>
+      </c>
+      <c r="J82" s="28">
+        <v>1</v>
+      </c>
+      <c r="K82" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="30">
+        <v>34</v>
+      </c>
+      <c r="B83" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83" s="30">
+        <v>3</v>
+      </c>
+      <c r="D83" s="27">
+        <v>2</v>
+      </c>
+      <c r="E83" s="27">
+        <v>1</v>
+      </c>
+      <c r="F83" s="27">
+        <v>2</v>
+      </c>
+      <c r="G83" s="27">
+        <v>1</v>
+      </c>
+      <c r="H83" s="27">
+        <v>1</v>
+      </c>
+      <c r="I83" s="27">
+        <v>1</v>
+      </c>
+      <c r="J83" s="28">
+        <v>1</v>
+      </c>
+      <c r="K83" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="30">
+        <v>42</v>
+      </c>
+      <c r="B84" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C84" s="30">
+        <v>1</v>
+      </c>
+      <c r="D84" s="27">
+        <v>1</v>
+      </c>
+      <c r="E84" s="27">
+        <v>1</v>
+      </c>
+      <c r="F84" s="27">
+        <v>1</v>
+      </c>
+      <c r="G84" s="27">
+        <v>1</v>
+      </c>
+      <c r="H84" s="27">
+        <v>1</v>
+      </c>
+      <c r="I84" s="27">
+        <v>1</v>
+      </c>
+      <c r="J84" s="28">
+        <v>1</v>
+      </c>
+      <c r="K84" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="30">
+        <v>52</v>
+      </c>
+      <c r="B85" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C85" s="30">
+        <v>2</v>
+      </c>
+      <c r="D85" s="27">
+        <v>3</v>
+      </c>
+      <c r="E85" s="27">
+        <v>1</v>
+      </c>
+      <c r="F85" s="27">
+        <v>3</v>
+      </c>
+      <c r="G85" s="27">
+        <v>1</v>
+      </c>
+      <c r="H85" s="27">
+        <v>1</v>
+      </c>
+      <c r="I85" s="27">
+        <v>1</v>
+      </c>
+      <c r="J85" s="28">
+        <v>1</v>
+      </c>
+      <c r="K85" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="30">
+        <v>69</v>
+      </c>
+      <c r="B86" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C86" s="30">
+        <v>1</v>
+      </c>
+      <c r="D86" s="27">
+        <v>1</v>
+      </c>
+      <c r="E86" s="27">
+        <v>1</v>
+      </c>
+      <c r="F86" s="27">
+        <v>1</v>
+      </c>
+      <c r="G86" s="27">
+        <v>1</v>
+      </c>
+      <c r="H86" s="27">
+        <v>1</v>
+      </c>
+      <c r="I86" s="27">
+        <v>1</v>
+      </c>
+      <c r="J86" s="28">
+        <v>1</v>
+      </c>
+      <c r="K86" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
+        <v>21</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C87" s="3">
+        <v>2</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87" s="4">
+        <v>1</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
+        <v>45</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88" s="4">
+        <v>1</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
+        <v>50</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C89" s="3">
+        <v>2</v>
+      </c>
+      <c r="D89">
+        <v>2</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>2</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89" s="4">
+        <v>1</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>30</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" s="3">
+        <v>1</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90" s="4">
+        <v>1</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
+        <v>70</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C91" s="3">
+        <v>2</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="J91" s="4">
+        <v>1</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
+        <v>35</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" s="3">
+        <v>2</v>
+      </c>
+      <c r="D92">
+        <v>2</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92">
+        <v>2</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92" s="4">
+        <v>1</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="30">
+        <v>28</v>
+      </c>
+      <c r="B93" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" s="30">
+        <v>1</v>
+      </c>
+      <c r="D93" s="27">
+        <v>1</v>
+      </c>
+      <c r="E93" s="27">
+        <v>1</v>
+      </c>
+      <c r="F93" s="27">
+        <v>1</v>
+      </c>
+      <c r="G93" s="27">
+        <v>1</v>
+      </c>
+      <c r="H93" s="27">
+        <v>1</v>
+      </c>
+      <c r="I93" s="27">
+        <v>1</v>
+      </c>
+      <c r="J93" s="28">
+        <v>1</v>
+      </c>
+      <c r="K93" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="30">
+        <v>31</v>
+      </c>
+      <c r="B94" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" s="30">
+        <v>1</v>
+      </c>
+      <c r="D94" s="27">
+        <v>1</v>
+      </c>
+      <c r="E94" s="27">
+        <v>1</v>
+      </c>
+      <c r="F94" s="27">
+        <v>1</v>
+      </c>
+      <c r="G94" s="27">
+        <v>1</v>
+      </c>
+      <c r="H94" s="27">
+        <v>1</v>
+      </c>
+      <c r="I94" s="27">
+        <v>1</v>
+      </c>
+      <c r="J94" s="28">
+        <v>1</v>
+      </c>
+      <c r="K94" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="30">
+        <v>40</v>
+      </c>
+      <c r="B95" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C95" s="30">
+        <v>5</v>
+      </c>
+      <c r="D95" s="27">
+        <v>3</v>
+      </c>
+      <c r="E95" s="27">
+        <v>2</v>
+      </c>
+      <c r="F95" s="27">
+        <v>4</v>
+      </c>
+      <c r="G95" s="27">
+        <v>1</v>
+      </c>
+      <c r="H95" s="27">
+        <v>4</v>
+      </c>
+      <c r="I95" s="27">
+        <v>4</v>
+      </c>
+      <c r="J95" s="28">
+        <v>4</v>
+      </c>
+      <c r="K95" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="30">
+        <v>66</v>
+      </c>
+      <c r="B96" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C96" s="30">
+        <v>1</v>
+      </c>
+      <c r="D96" s="27">
+        <v>1</v>
+      </c>
+      <c r="E96" s="27">
+        <v>1</v>
+      </c>
+      <c r="F96" s="27">
+        <v>1</v>
+      </c>
+      <c r="G96" s="27">
+        <v>1</v>
+      </c>
+      <c r="H96" s="27">
+        <v>1</v>
+      </c>
+      <c r="I96" s="27">
+        <v>1</v>
+      </c>
+      <c r="J96" s="28">
+        <v>1</v>
+      </c>
+      <c r="K96" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="30">
+        <v>67</v>
+      </c>
+      <c r="B97" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C97" s="30">
+        <v>5</v>
+      </c>
+      <c r="D97" s="27">
+        <v>4</v>
+      </c>
+      <c r="E97" s="27">
+        <v>1</v>
+      </c>
+      <c r="F97" s="27">
+        <v>4</v>
+      </c>
+      <c r="G97" s="27">
+        <v>1</v>
+      </c>
+      <c r="H97" s="27">
+        <v>2</v>
+      </c>
+      <c r="I97" s="27">
+        <v>3</v>
+      </c>
+      <c r="J97" s="28">
+        <v>2</v>
+      </c>
+      <c r="K97" s="28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="30">
+        <v>24</v>
+      </c>
+      <c r="B98" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" s="30">
+        <v>1</v>
+      </c>
+      <c r="D98" s="27">
+        <v>1</v>
+      </c>
+      <c r="E98" s="27">
+        <v>1</v>
+      </c>
+      <c r="F98" s="27">
+        <v>1</v>
+      </c>
+      <c r="G98" s="27">
+        <v>1</v>
+      </c>
+      <c r="H98" s="27">
+        <v>1</v>
+      </c>
+      <c r="I98" s="27">
+        <v>1</v>
+      </c>
+      <c r="J98" s="28">
+        <v>1</v>
+      </c>
+      <c r="K98" s="28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
+        <v>25</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" s="3">
+        <v>1</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99" s="4">
+        <v>1</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
+        <v>39</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C100" s="3">
+        <v>2</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="F100">
+        <v>2</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100" s="4">
+        <v>1</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="5">
+        <v>38</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C101" s="5">
+        <v>1</v>
+      </c>
+      <c r="D101" s="6">
+        <v>1</v>
+      </c>
+      <c r="E101" s="6">
+        <v>1</v>
+      </c>
+      <c r="F101" s="6">
+        <v>1</v>
+      </c>
+      <c r="G101" s="6">
+        <v>1</v>
+      </c>
+      <c r="H101" s="6">
+        <v>1</v>
+      </c>
+      <c r="I101" s="6">
+        <v>1</v>
+      </c>
+      <c r="J101" s="7">
+        <v>1</v>
+      </c>
+      <c r="K101" s="7" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
